--- a/screening/Cu_Removal_Screening.xlsx
+++ b/screening/Cu_Removal_Screening.xlsx
@@ -22,13 +22,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="+#,##0.0;-#,##0.0"/>
-    <numFmt numFmtId="166" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="$#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.##"/>
+    <numFmt numFmtId="167" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="$#,##0.0000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,12 +65,16 @@
       <sz val="11"/>
     </font>
     <font>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <i val="1"/>
       <color rgb="00996600"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -98,12 +103,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -191,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -240,10 +239,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -258,10 +254,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -276,139 +269,226 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -421,34 +501,86 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="2" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="2" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="168" fontId="2" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="2" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -2722,7 +2854,7 @@
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>Values are dGf in kJ/mol O2 (Ellingham convention).</t>
+          <t>Values are dGf in J/mol O2 (Ellingham convention). Divide by 1000 for kJ.</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2856,73 +2988,77 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F2" s="18" t="n">
-        <v>997.176410439688</v>
-      </c>
-      <c r="G2" s="18" t="n">
-        <v>1156.310100552693</v>
-      </c>
-      <c r="H2" s="18" t="n">
-        <v>1240.711951535208</v>
-      </c>
-      <c r="I2" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J2" s="20" t="inlineStr">
+      <c r="F2" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1000,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$B:$B,MATCH(1000,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="G2" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1500,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$B:$B,MATCH(1500,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="H2" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1800,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$B:$B,MATCH(1800,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="I2" s="17">
+        <f>IF(NOT(ISNUMBER(H2)),"TBD",IF(H2&gt;0,"No",IF(A2="CuO","Trivially","Yes")))</f>
+        <v/>
+      </c>
+      <c r="J2" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K2" s="21" t="inlineStr">
+      <c r="K2" s="20" t="inlineStr">
         <is>
           <t>SSUB3</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>CaO</t>
         </is>
       </c>
-      <c r="B3" s="23" t="n">
+      <c r="B3" s="22" t="n">
         <v>3.34</v>
       </c>
-      <c r="C3" s="23" t="n">
+      <c r="C3" s="22" t="n">
         <v>2613</v>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E3" s="23" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F3" s="24" t="n">
-        <v>870.2192184169537</v>
-      </c>
-      <c r="G3" s="24" t="n">
-        <v>836.4403201913545</v>
-      </c>
-      <c r="H3" s="24" t="n">
-        <v>791.3091397887691</v>
-      </c>
-      <c r="I3" s="25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J3" s="26" t="inlineStr">
+      <c r="F3" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1000,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$C:$C,MATCH(1000,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="G3" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1500,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$C:$C,MATCH(1500,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="H3" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1800,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$C:$C,MATCH(1800,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="I3" s="22">
+        <f>IF(NOT(ISNUMBER(H3)),"TBD",IF(H3&gt;0,"No",IF(A3="CuO","Trivially","Yes")))</f>
+        <v/>
+      </c>
+      <c r="J3" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K3" s="27" t="inlineStr">
+      <c r="K3" s="25" t="inlineStr">
         <is>
           <t>TCOX14</t>
         </is>
@@ -2950,73 +3086,77 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F4" s="18" t="n">
-        <v>812.9932359534887</v>
-      </c>
-      <c r="G4" s="18" t="n">
-        <v>795.1855288534199</v>
-      </c>
-      <c r="H4" s="18" t="n">
-        <v>766.2790754363556</v>
-      </c>
-      <c r="I4" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J4" s="20" t="inlineStr">
+      <c r="F4" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1000,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$D:$D,MATCH(1000,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="G4" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1500,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$D:$D,MATCH(1500,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="H4" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1800,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$D:$D,MATCH(1800,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="I4" s="17">
+        <f>IF(NOT(ISNUMBER(H4)),"TBD",IF(H4&gt;0,"No",IF(A4="CuO","Trivially","Yes")))</f>
+        <v/>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>Low-Moderate</t>
         </is>
       </c>
-      <c r="K4" s="21" t="inlineStr">
+      <c r="K4" s="20" t="inlineStr">
         <is>
           <t>TCOX14</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>MgO</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n">
+      <c r="B5" s="22" t="n">
         <v>3.58</v>
       </c>
-      <c r="C5" s="23" t="n">
+      <c r="C5" s="22" t="n">
         <v>2852</v>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F5" s="24" t="n">
-        <v>795.9526219778686</v>
-      </c>
-      <c r="G5" s="24" t="n">
-        <v>736.4880161626211</v>
-      </c>
-      <c r="H5" s="24" t="n">
-        <v>642.8620279630527</v>
-      </c>
-      <c r="I5" s="25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J5" s="26" t="inlineStr">
+      <c r="F5" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1000,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$E:$E,MATCH(1000,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="G5" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1500,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$E:$E,MATCH(1500,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="H5" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1800,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$E:$E,MATCH(1800,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="I5" s="22">
+        <f>IF(NOT(ISNUMBER(H5)),"TBD",IF(H5&gt;0,"No",IF(A5="CuO","Trivially","Yes")))</f>
+        <v/>
+      </c>
+      <c r="J5" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K5" s="27" t="inlineStr">
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t>TCOX14</t>
         </is>
@@ -3044,73 +3184,77 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F6" s="18" t="n">
-        <v>718.5932321662127</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>702.0665220139746</v>
-      </c>
-      <c r="H6" s="18" t="n">
-        <v>675.6992805726175</v>
-      </c>
-      <c r="I6" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J6" s="20" t="inlineStr">
+      <c r="F6" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1000,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$F:$F,MATCH(1000,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="G6" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1500,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$F:$F,MATCH(1500,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="H6" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1800,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$F:$F,MATCH(1800,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="I6" s="17">
+        <f>IF(NOT(ISNUMBER(H6)),"TBD",IF(H6&gt;0,"No",IF(A6="CuO","Trivially","Yes")))</f>
+        <v/>
+      </c>
+      <c r="J6" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K6" s="21" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t>TCOX14</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Al2O3</t>
         </is>
       </c>
-      <c r="B7" s="23" t="n">
+      <c r="B7" s="22" t="n">
         <v>3.95</v>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C7" s="22" t="n">
         <v>2072</v>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F7" s="24" t="n">
-        <v>716.7173113289498</v>
-      </c>
-      <c r="G7" s="24" t="n">
-        <v>682.6687092047364</v>
-      </c>
-      <c r="H7" s="24" t="n">
-        <v>644.8222226505188</v>
-      </c>
-      <c r="I7" s="25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J7" s="26" t="inlineStr">
+      <c r="F7" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1000,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$G:$G,MATCH(1000,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="G7" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1500,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$G:$G,MATCH(1500,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="H7" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1800,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$G:$G,MATCH(1800,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="I7" s="22">
+        <f>IF(NOT(ISNUMBER(H7)),"TBD",IF(H7&gt;0,"No",IF(A7="CuO","Trivially","Yes")))</f>
+        <v/>
+      </c>
+      <c r="J7" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K7" s="27" t="inlineStr">
+      <c r="K7" s="25" t="inlineStr">
         <is>
           <t>TCOX14</t>
         </is>
@@ -3138,73 +3282,77 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F8" s="18" t="n">
-        <v>569.3889463674802</v>
-      </c>
-      <c r="G8" s="18" t="n">
-        <v>556.6679052290083</v>
-      </c>
-      <c r="H8" s="18" t="n">
-        <v>531.2981945804858</v>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J8" s="20" t="inlineStr">
+      <c r="F8" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1000,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$H:$H,MATCH(1000,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="G8" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1500,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$H:$H,MATCH(1500,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="H8" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1800,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$H:$H,MATCH(1800,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="I8" s="17">
+        <f>IF(NOT(ISNUMBER(H8)),"TBD",IF(H8&gt;0,"No",IF(A8="CuO","Trivially","Yes")))</f>
+        <v/>
+      </c>
+      <c r="J8" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K8" s="21" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>TCOX14</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>SiO2</t>
         </is>
       </c>
-      <c r="B9" s="23" t="n">
+      <c r="B9" s="22" t="n">
         <v>2.65</v>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="22" t="n">
         <v>1713</v>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F9" s="24" t="n">
-        <v>539.3696799238344</v>
-      </c>
-      <c r="G9" s="24" t="n">
-        <v>529.4276545104799</v>
-      </c>
-      <c r="H9" s="24" t="n">
-        <v>502.720485707874</v>
-      </c>
-      <c r="I9" s="25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J9" s="26" t="inlineStr">
+      <c r="F9" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1000,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$I:$I,MATCH(1000,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="G9" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1500,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$I:$I,MATCH(1500,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="H9" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1800,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$I:$I,MATCH(1800,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="I9" s="22">
+        <f>IF(NOT(ISNUMBER(H9)),"TBD",IF(H9&gt;0,"No",IF(A9="CuO","Trivially","Yes")))</f>
+        <v/>
+      </c>
+      <c r="J9" s="24" t="inlineStr">
         <is>
           <t>Low (silicosis)</t>
         </is>
       </c>
-      <c r="K9" s="27" t="inlineStr">
+      <c r="K9" s="25" t="inlineStr">
         <is>
           <t>TCOX14</t>
         </is>
@@ -3232,73 +3380,77 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F10" s="18" t="n">
-        <v>434.0671356646179</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>433.903241534569</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>408.894023554667</v>
-      </c>
-      <c r="I10" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J10" s="20" t="inlineStr">
+      <c r="F10" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1000,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$J:$J,MATCH(1000,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="G10" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1500,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$J:$J,MATCH(1500,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="H10" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1800,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$J:$J,MATCH(1800,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="I10" s="17">
+        <f>IF(NOT(ISNUMBER(H10)),"TBD",IF(H10&gt;0,"No",IF(A10="CuO","Trivially","Yes")))</f>
+        <v/>
+      </c>
+      <c r="J10" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K10" s="21" t="inlineStr">
+      <c r="K10" s="20" t="inlineStr">
         <is>
           <t>TCOX14</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Cr2O3</t>
         </is>
       </c>
-      <c r="B11" s="23" t="n">
+      <c r="B11" s="22" t="n">
         <v>5.22</v>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="22" t="n">
         <v>2435</v>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F11" s="24" t="n">
-        <v>385.6932755397189</v>
-      </c>
-      <c r="G11" s="24" t="n">
-        <v>377.815074714703</v>
-      </c>
-      <c r="H11" s="24" t="n">
-        <v>354.838962051855</v>
-      </c>
-      <c r="I11" s="25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J11" s="26" t="inlineStr">
+      <c r="F11" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1000,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$K:$K,MATCH(1000,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="G11" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1500,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$K:$K,MATCH(1500,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="H11" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1800,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$K:$K,MATCH(1800,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="I11" s="22">
+        <f>IF(NOT(ISNUMBER(H11)),"TBD",IF(H11&gt;0,"No",IF(A11="CuO","Trivially","Yes")))</f>
+        <v/>
+      </c>
+      <c r="J11" s="24" t="inlineStr">
         <is>
           <t>Moderate (Cr VI)</t>
         </is>
       </c>
-      <c r="K11" s="27" t="inlineStr">
+      <c r="K11" s="25" t="inlineStr">
         <is>
           <t>TCOX14</t>
         </is>
@@ -3321,78 +3473,82 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E12" s="28" t="inlineStr">
+      <c r="E12" s="26" t="inlineStr">
         <is>
           <t>LIQUID</t>
         </is>
       </c>
-      <c r="F12" s="18" t="n">
-        <v>257.218656522464</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>266.9982607973439</v>
-      </c>
-      <c r="H12" s="18" t="n">
-        <v>259.4176758391675</v>
-      </c>
-      <c r="I12" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J12" s="20" t="inlineStr">
+      <c r="F12" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1000,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$L:$L,MATCH(1000,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="G12" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1500,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$L:$L,MATCH(1500,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="H12" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1800,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$L:$L,MATCH(1800,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="I12" s="17">
+        <f>IF(NOT(ISNUMBER(H12)),"TBD",IF(H12&gt;0,"No",IF(A12="CuO","Trivially","Yes")))</f>
+        <v/>
+      </c>
+      <c r="J12" s="19" t="inlineStr">
         <is>
           <t>HIGH - Carc. 1B</t>
         </is>
       </c>
-      <c r="K12" s="21" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>TCOX14</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>FeO</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n">
+      <c r="B13" s="22" t="n">
         <v>5.74</v>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C13" s="22" t="n">
         <v>1377</v>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E13" s="29" t="inlineStr">
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>LIQUID</t>
         </is>
       </c>
-      <c r="F13" s="24" t="n">
-        <v>220.3786238510149</v>
-      </c>
-      <c r="G13" s="24" t="n">
-        <v>230.7342226643402</v>
-      </c>
-      <c r="H13" s="24" t="n">
-        <v>213.8079839998335</v>
-      </c>
-      <c r="I13" s="25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J13" s="26" t="inlineStr">
+      <c r="F13" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1000,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$M:$M,MATCH(1000,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="G13" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1500,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$M:$M,MATCH(1500,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="H13" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1800,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$M:$M,MATCH(1800,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="I13" s="22">
+        <f>IF(NOT(ISNUMBER(H13)),"TBD",IF(H13&gt;0,"No",IF(A13="CuO","Trivially","Yes")))</f>
+        <v/>
+      </c>
+      <c r="J13" s="24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K13" s="27" t="inlineStr">
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t>TCOX14</t>
         </is>
@@ -3420,73 +3576,77 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F14" s="18" t="n">
-        <v>134.8996376127765</v>
-      </c>
-      <c r="G14" s="18" t="n">
-        <v>141.2803567226338</v>
-      </c>
-      <c r="H14" s="18" t="n">
-        <v>126.618759676311</v>
-      </c>
-      <c r="I14" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J14" s="20" t="inlineStr">
+      <c r="F14" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1000,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$N:$N,MATCH(1000,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="G14" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1500,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$N:$N,MATCH(1500,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="H14" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1800,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$N:$N,MATCH(1800,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="I14" s="17">
+        <f>IF(NOT(ISNUMBER(H14)),"TBD",IF(H14&gt;0,"No",IF(A14="CuO","Trivially","Yes")))</f>
+        <v/>
+      </c>
+      <c r="J14" s="19" t="inlineStr">
         <is>
           <t>HIGH - Carc. 1B</t>
         </is>
       </c>
-      <c r="K14" s="21" t="inlineStr">
+      <c r="K14" s="20" t="inlineStr">
         <is>
           <t>TCOX14</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>NiO</t>
         </is>
       </c>
-      <c r="B15" s="23" t="n">
+      <c r="B15" s="22" t="n">
         <v>6.67</v>
       </c>
-      <c r="C15" s="23" t="n">
+      <c r="C15" s="22" t="n">
         <v>1955</v>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F15" s="24" t="n">
-        <v>107.5408866133889</v>
-      </c>
-      <c r="G15" s="24" t="n">
-        <v>99.5065630489029</v>
-      </c>
-      <c r="H15" s="24" t="n">
-        <v>76.02293325153424</v>
-      </c>
-      <c r="I15" s="25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J15" s="26" t="inlineStr">
+      <c r="F15" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1000,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$O:$O,MATCH(1000,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="G15" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1500,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$O:$O,MATCH(1500,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="H15" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1800,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$O:$O,MATCH(1800,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="I15" s="22">
+        <f>IF(NOT(ISNUMBER(H15)),"TBD",IF(H15&gt;0,"No",IF(A15="CuO","Trivially","Yes")))</f>
+        <v/>
+      </c>
+      <c r="J15" s="24" t="inlineStr">
         <is>
           <t>HIGH - IARC Grp 1</t>
         </is>
       </c>
-      <c r="K15" s="27" t="inlineStr">
+      <c r="K15" s="25" t="inlineStr">
         <is>
           <t>TCOX14</t>
         </is>
@@ -3509,129 +3669,131 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E16" s="28" t="inlineStr">
+      <c r="E16" s="26" t="inlineStr">
         <is>
           <t>LIQUID</t>
         </is>
       </c>
-      <c r="F16" s="30" t="n">
-        <v>-34.73941666031201</v>
-      </c>
-      <c r="G16" s="18" t="n">
-        <v>81.02583535269237</v>
-      </c>
-      <c r="H16" s="18" t="n">
-        <v>136.1552920352077</v>
-      </c>
-      <c r="I16" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J16" s="20" t="inlineStr">
+      <c r="F16" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1000,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$P:$P,MATCH(1000,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="G16" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1500,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$P:$P,MATCH(1500,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="H16" s="18">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1800,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$P:$P,MATCH(1800,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="I16" s="17">
+        <f>IF(NOT(ISNUMBER(H16)),"TBD",IF(H16&gt;0,"No",IF(A16="CuO","Trivially","Yes")))</f>
+        <v/>
+      </c>
+      <c r="J16" s="19" t="inlineStr">
         <is>
           <t>HIGH - neurotoxin</t>
         </is>
       </c>
-      <c r="K16" s="21" t="inlineStr">
+      <c r="K16" s="20" t="inlineStr">
         <is>
           <t>SSUB3</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>B2O3</t>
         </is>
       </c>
-      <c r="B17" s="23" t="n">
+      <c r="B17" s="22" t="n">
         <v>2.55</v>
       </c>
-      <c r="C17" s="23" t="n">
+      <c r="C17" s="22" t="n">
         <v>450</v>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E17" s="29" t="inlineStr">
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t>LIQUID</t>
         </is>
       </c>
-      <c r="F17" s="31" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G17" s="31" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H17" s="24" t="n">
-        <v>481.1041698284617</v>
-      </c>
-      <c r="I17" s="25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J17" s="26" t="inlineStr">
+      <c r="F17" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1000,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$S:$S,MATCH(1000,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="G17" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1500,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$S:$S,MATCH(1500,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="H17" s="23">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1800,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$S:$S,MATCH(1800,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="I17" s="22">
+        <f>IF(NOT(ISNUMBER(H17)),"TBD",IF(H17&gt;0,"No",IF(A17="CuO","Trivially","Yes")))</f>
+        <v/>
+      </c>
+      <c r="J17" s="24" t="inlineStr">
         <is>
           <t>Moderate - Repr.1B</t>
         </is>
       </c>
-      <c r="K17" s="27" t="inlineStr">
+      <c r="K17" s="25" t="inlineStr">
         <is>
           <t>TCOX14</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>CuO</t>
         </is>
       </c>
-      <c r="B18" s="33" t="n">
+      <c r="B18" s="29" t="n">
         <v>6.31</v>
       </c>
-      <c r="C18" s="33" t="n">
+      <c r="C18" s="29" t="n">
         <v>1326</v>
       </c>
-      <c r="D18" s="33" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E18" s="34" t="inlineStr">
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t>LIQUID</t>
         </is>
       </c>
-      <c r="F18" s="35" t="n">
-        <v>-58.80589050160665</v>
-      </c>
-      <c r="G18" s="35" t="n">
-        <v>-51.73128594025172</v>
-      </c>
-      <c r="H18" s="35" t="n">
-        <v>-40.99015583836951</v>
-      </c>
-      <c r="I18" s="33" t="inlineStr">
-        <is>
-          <t>Trivially</t>
-        </is>
-      </c>
-      <c r="J18" s="36" t="inlineStr">
+      <c r="F18" s="31">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1000,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$R:$R,MATCH(1000,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="G18" s="31">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1500,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$R:$R,MATCH(1500,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="H18" s="31">
+        <f>IFERROR((INDEX('Formation Energies'!$Q:$Q,MATCH(1800,'Formation Energies'!$A:$A,0))-INDEX('Formation Energies'!$R:$R,MATCH(1800,'Formation Energies'!$A:$A,0)))/1000,"TBD")</f>
+        <v/>
+      </c>
+      <c r="I18" s="29">
+        <f>IF(NOT(ISNUMBER(H18)),"TBD",IF(H18&gt;0,"No",IF(A18="CuO","Trivially","Yes")))</f>
+        <v/>
+      </c>
+      <c r="J18" s="32" t="inlineStr">
         <is>
           <t>Moderate - aquatic</t>
         </is>
       </c>
-      <c r="K18" s="37" t="inlineStr">
+      <c r="K18" s="33" t="inlineStr">
         <is>
           <t>TCOX14</t>
         </is>
@@ -3654,32 +3816,70 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>Molten steel density ~ 7.0 g/cm3 at 1600C. Oxides lighter than steel float.</t>
+          <t>FORMULA CELLS: Cols F-H use INDEX/MATCH referencing 'Formation Energies' tab.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>Red values = UNFAVORABLE (oxide too stable). Green = Cu can reduce.</t>
+          <t>Col I verdict is an IF() formula based on Col H value.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>CuO: Cu2O -&gt; CuO is further Cu oxidation, not useful for removal.</t>
+          <t>Total formula cells: 68 (3 dG + 1 verdict per oxide).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
+          <t>Molten steel density ~ 7.0 g/cm3 at 1600C. Oxides lighter than steel float.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>CuO: Cu2O -&gt; CuO is further Cu oxidation, not useful for removal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
           <t>Conclusion: Cu cannot directly reduce ANY useful ceramic oxide at steelmaking temps.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="F2:F18">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThanOrEqual" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G18">
+    <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="lessThanOrEqual" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H18">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="lessThanOrEqual" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3690,7 +3890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3781,162 +3981,165 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="32" t="inlineStr">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>CuAl2O4</t>
         </is>
       </c>
-      <c r="B2" s="36" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>Copper aluminate spinel</t>
         </is>
       </c>
-      <c r="C2" s="36" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>Spinel</t>
         </is>
       </c>
-      <c r="D2" s="36" t="inlineStr">
+      <c r="D2" s="32" t="inlineStr">
         <is>
           <t>Cu + Al2O3 + 0.5 O2 -&gt; CuAl2O4</t>
         </is>
       </c>
-      <c r="E2" s="33" t="n">
+      <c r="E2" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="36" t="inlineStr">
+      <c r="F2" s="32" t="inlineStr">
         <is>
           <t>Al2O3</t>
         </is>
       </c>
-      <c r="G2" s="33" t="n">
+      <c r="G2" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="33" t="n">
+      <c r="H2" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="I2" s="33" t="n">
+      <c r="I2" s="29" t="n">
         <v>0.5</v>
       </c>
-      <c r="J2" s="33" t="n">
+      <c r="J2" s="29">
+        <f>I2*2</f>
+        <v/>
+      </c>
+      <c r="K2" s="29">
+        <f>E2+G2*H2+J2</f>
+        <v/>
+      </c>
+      <c r="L2" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="M2" s="13">
+        <f>IF(ABS(K2-L2)&lt;0.01,"YES","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>CuAlO2</t>
+        </is>
+      </c>
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>Delafossite</t>
+        </is>
+      </c>
+      <c r="C3" s="35" t="inlineStr">
+        <is>
+          <t>Delafossite</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="inlineStr">
+        <is>
+          <t>Cu + 0.5 Al2O3 + 0.25 O2 -&gt; CuAlO2</t>
+        </is>
+      </c>
+      <c r="E3" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="K2" s="33" t="n">
+      <c r="F3" s="35" t="inlineStr">
+        <is>
+          <t>Al2O3</t>
+        </is>
+      </c>
+      <c r="G3" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H3" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" s="36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J3" s="36">
+        <f>I3*2</f>
+        <v/>
+      </c>
+      <c r="K3" s="36">
+        <f>E3+G3*H3+J3</f>
+        <v/>
+      </c>
+      <c r="L3" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="M3" s="37">
+        <f>IF(ABS(K3-L3)&lt;0.01,"YES","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="38" t="inlineStr">
+        <is>
+          <t>CuCr2O4</t>
+        </is>
+      </c>
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>Copper chromite spinel</t>
+        </is>
+      </c>
+      <c r="C4" s="39" t="inlineStr">
+        <is>
+          <t>Spinel</t>
+        </is>
+      </c>
+      <c r="D4" s="39" t="inlineStr">
+        <is>
+          <t>Cu + Cr2O3 + 0.5 O2 -&gt; CuCr2O4</t>
+        </is>
+      </c>
+      <c r="E4" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="39" t="inlineStr">
+        <is>
+          <t>Cr2O3</t>
+        </is>
+      </c>
+      <c r="G4" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J4" s="40">
+        <f>I4*2</f>
+        <v/>
+      </c>
+      <c r="K4" s="40">
+        <f>E4+G4*H4+J4</f>
+        <v/>
+      </c>
+      <c r="L4" s="40" t="n">
         <v>7</v>
       </c>
-      <c r="L2" s="33" t="n">
-        <v>7</v>
-      </c>
-      <c r="M2" s="38" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="39" t="inlineStr">
-        <is>
-          <t>CuAlO2</t>
-        </is>
-      </c>
-      <c r="B3" s="40" t="inlineStr">
-        <is>
-          <t>Delafossite</t>
-        </is>
-      </c>
-      <c r="C3" s="40" t="inlineStr">
-        <is>
-          <t>Delafossite</t>
-        </is>
-      </c>
-      <c r="D3" s="40" t="inlineStr">
-        <is>
-          <t>Cu + 0.5 Al2O3 + 0.25 O2 -&gt; CuAlO2</t>
-        </is>
-      </c>
-      <c r="E3" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="40" t="inlineStr">
-        <is>
-          <t>Al2O3</t>
-        </is>
-      </c>
-      <c r="G3" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H3" s="41" t="n">
-        <v>5</v>
-      </c>
-      <c r="I3" s="41" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J3" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K3" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="L3" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="M3" s="42" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="43" t="inlineStr">
-        <is>
-          <t>CuCr2O4</t>
-        </is>
-      </c>
-      <c r="B4" s="44" t="inlineStr">
-        <is>
-          <t>Copper chromite spinel</t>
-        </is>
-      </c>
-      <c r="C4" s="44" t="inlineStr">
-        <is>
-          <t>Spinel</t>
-        </is>
-      </c>
-      <c r="D4" s="44" t="inlineStr">
-        <is>
-          <t>Cu + Cr2O3 + 0.5 O2 -&gt; CuCr2O4</t>
-        </is>
-      </c>
-      <c r="E4" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="44" t="inlineStr">
-        <is>
-          <t>Cr2O3</t>
-        </is>
-      </c>
-      <c r="G4" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" s="45" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J4" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="45" t="n">
-        <v>7</v>
-      </c>
-      <c r="L4" s="45" t="n">
-        <v>7</v>
-      </c>
-      <c r="M4" s="46" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
+      <c r="M4" s="41">
+        <f>IF(ABS(K4-L4)&lt;0.01,"YES","NO")</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -3945,17 +4148,17 @@
           <t>CuMn2O4</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Copper manganite spinel</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>Spinel</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Cu + 2MnO + O2 -&gt; CuMn2O4</t>
         </is>
@@ -3963,7 +4166,7 @@
       <c r="E5" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>MnO</t>
         </is>
@@ -3977,19 +4180,20 @@
       <c r="I5" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="17" t="n">
-        <v>7</v>
+      <c r="J5" s="17">
+        <f>I5*2</f>
+        <v/>
+      </c>
+      <c r="K5" s="17">
+        <f>E5+G5*H5+J5</f>
+        <v/>
       </c>
       <c r="L5" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="M5" s="47" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
+      <c r="M5" s="6">
+        <f>IF(ABS(K5-L5)&lt;0.01,"YES","NO")</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -3998,17 +4202,17 @@
           <t>CuFe2O4</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Copper ferrite spinel</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>Spinel</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>Cu + 2FeO + O2 -&gt; CuFe2O4</t>
         </is>
@@ -4016,7 +4220,7 @@
       <c r="E6" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>FeO</t>
         </is>
@@ -4030,390 +4234,398 @@
       <c r="I6" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" s="17" t="n">
-        <v>7</v>
+      <c r="J6" s="17">
+        <f>I6*2</f>
+        <v/>
+      </c>
+      <c r="K6" s="17">
+        <f>E6+G6*H6+J6</f>
+        <v/>
       </c>
       <c r="L6" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="M6" s="47" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
+      <c r="M6" s="6">
+        <f>IF(ABS(K6-L6)&lt;0.01,"YES","NO")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>CuCo2O4</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Copper cobaltite spinel</t>
         </is>
       </c>
-      <c r="C7" s="36" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>Spinel</t>
         </is>
       </c>
-      <c r="D7" s="36" t="inlineStr">
+      <c r="D7" s="32" t="inlineStr">
         <is>
           <t>Cu + 2CoO + O2 -&gt; CuCo2O4</t>
         </is>
       </c>
-      <c r="E7" s="33" t="n">
+      <c r="E7" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="36" t="inlineStr">
+      <c r="F7" s="32" t="inlineStr">
         <is>
           <t>CoO</t>
         </is>
       </c>
-      <c r="G7" s="33" t="n">
+      <c r="G7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="33" t="n">
+      <c r="H7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="33" t="n">
+      <c r="I7" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="33" t="n">
+      <c r="J7" s="29">
+        <f>I7*2</f>
+        <v/>
+      </c>
+      <c r="K7" s="29">
+        <f>E7+G7*H7+J7</f>
+        <v/>
+      </c>
+      <c r="L7" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" s="13">
+        <f>IF(ABS(K7-L7)&lt;0.01,"YES","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="42" t="inlineStr">
+        <is>
+          <t>CuV2O6</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>Copper vanadate</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>Vanadate</t>
+        </is>
+      </c>
+      <c r="D8" s="43" t="inlineStr">
+        <is>
+          <t>Cu + V2O5 + 0.5 O2 -&gt; CuV2O6</t>
+        </is>
+      </c>
+      <c r="E8" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="43" t="inlineStr">
+        <is>
+          <t>V2O5</t>
+        </is>
+      </c>
+      <c r="G8" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="44" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" s="44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J8" s="44">
+        <f>I8*2</f>
+        <v/>
+      </c>
+      <c r="K8" s="44">
+        <f>E8+G8*H8+J8</f>
+        <v/>
+      </c>
+      <c r="L8" s="44" t="n">
+        <v>9</v>
+      </c>
+      <c r="M8" s="45">
+        <f>IF(ABS(K8-L8)&lt;0.01,"YES","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="46" t="inlineStr">
+        <is>
+          <t>Cu3V2O8</t>
+        </is>
+      </c>
+      <c r="B9" s="47" t="inlineStr">
+        <is>
+          <t>Copper orthovanadate</t>
+        </is>
+      </c>
+      <c r="C9" s="47" t="inlineStr">
+        <is>
+          <t>Vanadate</t>
+        </is>
+      </c>
+      <c r="D9" s="47" t="inlineStr">
+        <is>
+          <t>3Cu + V2O5 + 1.5 O2 -&gt; Cu3V2O8</t>
+        </is>
+      </c>
+      <c r="E9" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="47" t="inlineStr">
+        <is>
+          <t>V2O5</t>
+        </is>
+      </c>
+      <c r="G9" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="48" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" s="48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J9" s="48">
+        <f>I9*2</f>
+        <v/>
+      </c>
+      <c r="K9" s="48">
+        <f>E9+G9*H9+J9</f>
+        <v/>
+      </c>
+      <c r="L9" s="48" t="n">
+        <v>13</v>
+      </c>
+      <c r="M9" s="49">
+        <f>IF(ABS(K9-L9)&lt;0.01,"YES","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="50" t="inlineStr">
+        <is>
+          <t>CuTiO3</t>
+        </is>
+      </c>
+      <c r="B10" s="51" t="inlineStr">
+        <is>
+          <t>Copper titanate</t>
+        </is>
+      </c>
+      <c r="C10" s="51" t="inlineStr">
+        <is>
+          <t>Titanate</t>
+        </is>
+      </c>
+      <c r="D10" s="51" t="inlineStr">
+        <is>
+          <t>Cu + TiO2 + 0.5 O2 -&gt; CuTiO3</t>
+        </is>
+      </c>
+      <c r="E10" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="51" t="inlineStr">
+        <is>
+          <t>TiO2</t>
+        </is>
+      </c>
+      <c r="G10" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J10" s="52">
+        <f>I10*2</f>
+        <v/>
+      </c>
+      <c r="K10" s="52">
+        <f>E10+G10*H10+J10</f>
+        <v/>
+      </c>
+      <c r="L10" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" s="53">
+        <f>IF(ABS(K10-L10)&lt;0.01,"YES","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>CuSiO3</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>Copper metasilicate</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>Silicate</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="inlineStr">
+        <is>
+          <t>Cu + SiO2 + 0.5 O2 -&gt; CuSiO3</t>
+        </is>
+      </c>
+      <c r="E11" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="43" t="inlineStr">
+        <is>
+          <t>SiO2</t>
+        </is>
+      </c>
+      <c r="G11" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J11" s="44">
+        <f>I11*2</f>
+        <v/>
+      </c>
+      <c r="K11" s="44">
+        <f>E11+G11*H11+J11</f>
+        <v/>
+      </c>
+      <c r="L11" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="M11" s="45">
+        <f>IF(ABS(K11-L11)&lt;0.01,"YES","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="46" t="inlineStr">
+        <is>
+          <t>Cu2SiO4</t>
+        </is>
+      </c>
+      <c r="B12" s="47" t="inlineStr">
+        <is>
+          <t>Copper orthosilicate</t>
+        </is>
+      </c>
+      <c r="C12" s="47" t="inlineStr">
+        <is>
+          <t>Silicate</t>
+        </is>
+      </c>
+      <c r="D12" s="47" t="inlineStr">
+        <is>
+          <t>2Cu + SiO2 + O2 -&gt; Cu2SiO4</t>
+        </is>
+      </c>
+      <c r="E12" s="48" t="n">
         <v>2</v>
       </c>
-      <c r="K7" s="33" t="n">
+      <c r="F12" s="47" t="inlineStr">
+        <is>
+          <t>SiO2</t>
+        </is>
+      </c>
+      <c r="G12" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="48">
+        <f>I12*2</f>
+        <v/>
+      </c>
+      <c r="K12" s="48">
+        <f>E12+G12*H12+J12</f>
+        <v/>
+      </c>
+      <c r="L12" s="48" t="n">
         <v>7</v>
       </c>
-      <c r="L7" s="33" t="n">
-        <v>7</v>
-      </c>
-      <c r="M7" s="38" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="48" t="inlineStr">
-        <is>
-          <t>CuV2O6</t>
-        </is>
-      </c>
-      <c r="B8" s="49" t="inlineStr">
-        <is>
-          <t>Copper vanadate</t>
-        </is>
-      </c>
-      <c r="C8" s="49" t="inlineStr">
-        <is>
-          <t>Vanadate</t>
-        </is>
-      </c>
-      <c r="D8" s="49" t="inlineStr">
-        <is>
-          <t>Cu + V2O5 + 0.5 O2 -&gt; CuV2O6</t>
-        </is>
-      </c>
-      <c r="E8" s="50" t="n">
+      <c r="M12" s="49">
+        <f>IF(ABS(K12-L12)&lt;0.01,"YES","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="38" t="inlineStr">
+        <is>
+          <t>CuMgO2</t>
+        </is>
+      </c>
+      <c r="B13" s="39" t="inlineStr">
+        <is>
+          <t>Copper magnesioxide (hyp.)</t>
+        </is>
+      </c>
+      <c r="C13" s="39" t="inlineStr">
+        <is>
+          <t>Hypothetical</t>
+        </is>
+      </c>
+      <c r="D13" s="39" t="inlineStr">
+        <is>
+          <t>Cu + MgO + 0.5 O2 -&gt; CuMgO2</t>
+        </is>
+      </c>
+      <c r="E13" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="49" t="inlineStr">
-        <is>
-          <t>V2O5</t>
-        </is>
-      </c>
-      <c r="G8" s="50" t="n">
+      <c r="F13" s="39" t="inlineStr">
+        <is>
+          <t>MgO</t>
+        </is>
+      </c>
+      <c r="G13" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="I8" s="50" t="n">
+      <c r="H13" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="J8" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="50" t="n">
-        <v>9</v>
-      </c>
-      <c r="L8" s="50" t="n">
-        <v>9</v>
-      </c>
-      <c r="M8" s="51" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="52" t="inlineStr">
-        <is>
-          <t>Cu3V2O8</t>
-        </is>
-      </c>
-      <c r="B9" s="53" t="inlineStr">
-        <is>
-          <t>Copper orthovanadate</t>
-        </is>
-      </c>
-      <c r="C9" s="53" t="inlineStr">
-        <is>
-          <t>Vanadate</t>
-        </is>
-      </c>
-      <c r="D9" s="53" t="inlineStr">
-        <is>
-          <t>3Cu + V2O5 + 1.5 O2 -&gt; Cu3V2O8</t>
-        </is>
-      </c>
-      <c r="E9" s="54" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="53" t="inlineStr">
-        <is>
-          <t>V2O5</t>
-        </is>
-      </c>
-      <c r="G9" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="54" t="n">
-        <v>7</v>
-      </c>
-      <c r="I9" s="54" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J9" s="54" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" s="54" t="n">
-        <v>13</v>
-      </c>
-      <c r="L9" s="54" t="n">
-        <v>13</v>
-      </c>
-      <c r="M9" s="55" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="56" t="inlineStr">
-        <is>
-          <t>CuTiO3</t>
-        </is>
-      </c>
-      <c r="B10" s="57" t="inlineStr">
-        <is>
-          <t>Copper titanate</t>
-        </is>
-      </c>
-      <c r="C10" s="57" t="inlineStr">
-        <is>
-          <t>Titanate</t>
-        </is>
-      </c>
-      <c r="D10" s="57" t="inlineStr">
-        <is>
-          <t>Cu + TiO2 + 0.5 O2 -&gt; CuTiO3</t>
-        </is>
-      </c>
-      <c r="E10" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="57" t="inlineStr">
-        <is>
-          <t>TiO2</t>
-        </is>
-      </c>
-      <c r="G10" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="58" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" s="58" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J10" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="58" t="n">
-        <v>5</v>
-      </c>
-      <c r="L10" s="58" t="n">
-        <v>5</v>
-      </c>
-      <c r="M10" s="59" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="48" t="inlineStr">
-        <is>
-          <t>CuSiO3</t>
-        </is>
-      </c>
-      <c r="B11" s="49" t="inlineStr">
-        <is>
-          <t>Copper metasilicate</t>
-        </is>
-      </c>
-      <c r="C11" s="49" t="inlineStr">
-        <is>
-          <t>Silicate</t>
-        </is>
-      </c>
-      <c r="D11" s="49" t="inlineStr">
-        <is>
-          <t>Cu + SiO2 + 0.5 O2 -&gt; CuSiO3</t>
-        </is>
-      </c>
-      <c r="E11" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="49" t="inlineStr">
-        <is>
-          <t>SiO2</t>
-        </is>
-      </c>
-      <c r="G11" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" s="50" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J11" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="L11" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M11" s="51" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="52" t="inlineStr">
-        <is>
-          <t>Cu2SiO4</t>
-        </is>
-      </c>
-      <c r="B12" s="53" t="inlineStr">
-        <is>
-          <t>Copper orthosilicate</t>
-        </is>
-      </c>
-      <c r="C12" s="53" t="inlineStr">
-        <is>
-          <t>Silicate</t>
-        </is>
-      </c>
-      <c r="D12" s="53" t="inlineStr">
-        <is>
-          <t>2Cu + SiO2 + O2 -&gt; Cu2SiO4</t>
-        </is>
-      </c>
-      <c r="E12" s="54" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="53" t="inlineStr">
-        <is>
-          <t>SiO2</t>
-        </is>
-      </c>
-      <c r="G12" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="54" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="54" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" s="54" t="n">
-        <v>7</v>
-      </c>
-      <c r="L12" s="54" t="n">
-        <v>7</v>
-      </c>
-      <c r="M12" s="55" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="43" t="inlineStr">
-        <is>
-          <t>CuMgO2</t>
-        </is>
-      </c>
-      <c r="B13" s="44" t="inlineStr">
-        <is>
-          <t>Copper magnesioxide (hyp.)</t>
-        </is>
-      </c>
-      <c r="C13" s="44" t="inlineStr">
-        <is>
-          <t>Hypothetical</t>
-        </is>
-      </c>
-      <c r="D13" s="44" t="inlineStr">
-        <is>
-          <t>Cu + MgO + 0.5 O2 -&gt; CuMgO2</t>
-        </is>
-      </c>
-      <c r="E13" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="44" t="inlineStr">
-        <is>
-          <t>MgO</t>
-        </is>
-      </c>
-      <c r="G13" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="45" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J13" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" s="45" t="n">
+      <c r="J13" s="40">
+        <f>I13*2</f>
+        <v/>
+      </c>
+      <c r="K13" s="40">
+        <f>E13+G13*H13+J13</f>
+        <v/>
+      </c>
+      <c r="L13" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="L13" s="45" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" s="46" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
+      <c r="M13" s="41">
+        <f>IF(ABS(K13-L13)&lt;0.01,"YES","NO")</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -4422,17 +4634,17 @@
           <t>CuCaO2</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>Copper calcioxide (hyp.)</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>Hypothetical</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>Cu + CaO + 0.5 O2 -&gt; CuCaO2</t>
         </is>
@@ -4440,7 +4652,7 @@
       <c r="E14" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>CaO</t>
         </is>
@@ -4454,329 +4666,357 @@
       <c r="I14" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="J14" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="17" t="n">
-        <v>4</v>
+      <c r="J14" s="17">
+        <f>I14*2</f>
+        <v/>
+      </c>
+      <c r="K14" s="17">
+        <f>E14+G14*H14+J14</f>
+        <v/>
       </c>
       <c r="L14" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="M14" s="47" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
+      <c r="M14" s="6">
+        <f>IF(ABS(K14-L14)&lt;0.01,"YES","NO")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>CuZrO3</t>
         </is>
       </c>
-      <c r="B15" s="36" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>Copper zirconate (hyp.)</t>
         </is>
       </c>
-      <c r="C15" s="36" t="inlineStr">
+      <c r="C15" s="32" t="inlineStr">
         <is>
           <t>Hypothetical</t>
         </is>
       </c>
-      <c r="D15" s="36" t="inlineStr">
+      <c r="D15" s="32" t="inlineStr">
         <is>
           <t>Cu + ZrO2 + 0.5 O2 -&gt; CuZrO3</t>
         </is>
       </c>
-      <c r="E15" s="33" t="n">
+      <c r="E15" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="36" t="inlineStr">
+      <c r="F15" s="32" t="inlineStr">
         <is>
           <t>ZrO2</t>
         </is>
       </c>
-      <c r="G15" s="33" t="n">
+      <c r="G15" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="33" t="n">
+      <c r="H15" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="I15" s="33" t="n">
+      <c r="I15" s="29" t="n">
         <v>0.5</v>
       </c>
-      <c r="J15" s="33" t="n">
+      <c r="J15" s="29">
+        <f>I15*2</f>
+        <v/>
+      </c>
+      <c r="K15" s="29">
+        <f>E15+G15*H15+J15</f>
+        <v/>
+      </c>
+      <c r="L15" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="M15" s="13">
+        <f>IF(ABS(K15-L15)&lt;0.01,"YES","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="42" t="inlineStr">
+        <is>
+          <t>CuNiO2</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>Copper nickelate</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="D16" s="43" t="inlineStr">
+        <is>
+          <t>Cu + NiO + 0.5 O2 -&gt; CuNiO2</t>
+        </is>
+      </c>
+      <c r="E16" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="K15" s="33" t="n">
+      <c r="F16" s="43" t="inlineStr">
+        <is>
+          <t>NiO</t>
+        </is>
+      </c>
+      <c r="G16" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J16" s="44">
+        <f>I16*2</f>
+        <v/>
+      </c>
+      <c r="K16" s="44">
+        <f>E16+G16*H16+J16</f>
+        <v/>
+      </c>
+      <c r="L16" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="M16" s="45">
+        <f>IF(ABS(K16-L16)&lt;0.01,"YES","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="46" t="inlineStr">
+        <is>
+          <t>CuLaO2</t>
+        </is>
+      </c>
+      <c r="B17" s="47" t="inlineStr">
+        <is>
+          <t>Copper lanthanum oxide</t>
+        </is>
+      </c>
+      <c r="C17" s="47" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="D17" s="47" t="inlineStr">
+        <is>
+          <t>Cu + 0.5 La2O3 + 0.25 O2 -&gt; CuLaO2</t>
+        </is>
+      </c>
+      <c r="E17" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="47" t="inlineStr">
+        <is>
+          <t>La2O3</t>
+        </is>
+      </c>
+      <c r="G17" s="48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H17" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="L15" s="33" t="n">
+      <c r="I17" s="48" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J17" s="48">
+        <f>I17*2</f>
+        <v/>
+      </c>
+      <c r="K17" s="48">
+        <f>E17+G17*H17+J17</f>
+        <v/>
+      </c>
+      <c r="L17" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" s="49">
+        <f>IF(ABS(K17-L17)&lt;0.01,"YES","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="50" t="inlineStr">
+        <is>
+          <t>CuCeO3</t>
+        </is>
+      </c>
+      <c r="B18" s="51" t="inlineStr">
+        <is>
+          <t>Copper cerate (hyp.)</t>
+        </is>
+      </c>
+      <c r="C18" s="51" t="inlineStr">
+        <is>
+          <t>Hypothetical</t>
+        </is>
+      </c>
+      <c r="D18" s="51" t="inlineStr">
+        <is>
+          <t>Cu + CeO2 + 0.5 O2 -&gt; CuCeO3</t>
+        </is>
+      </c>
+      <c r="E18" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="51" t="inlineStr">
+        <is>
+          <t>CeO2</t>
+        </is>
+      </c>
+      <c r="G18" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J18" s="52">
+        <f>I18*2</f>
+        <v/>
+      </c>
+      <c r="K18" s="52">
+        <f>E18+G18*H18+J18</f>
+        <v/>
+      </c>
+      <c r="L18" s="52" t="n">
         <v>5</v>
       </c>
-      <c r="M15" s="38" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="48" t="inlineStr">
-        <is>
-          <t>CuNiO2</t>
-        </is>
-      </c>
-      <c r="B16" s="49" t="inlineStr">
-        <is>
-          <t>Copper nickelate</t>
-        </is>
-      </c>
-      <c r="C16" s="49" t="inlineStr">
-        <is>
-          <t>Compound</t>
-        </is>
-      </c>
-      <c r="D16" s="49" t="inlineStr">
-        <is>
-          <t>Cu + NiO + 0.5 O2 -&gt; CuNiO2</t>
-        </is>
-      </c>
-      <c r="E16" s="50" t="n">
+      <c r="M18" s="53">
+        <f>IF(ABS(K18-L18)&lt;0.01,"YES","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="34" t="inlineStr">
+        <is>
+          <t>CuB2O4</t>
+        </is>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>Copper borate</t>
+        </is>
+      </c>
+      <c r="C19" s="35" t="inlineStr">
+        <is>
+          <t>Borate</t>
+        </is>
+      </c>
+      <c r="D19" s="35" t="inlineStr">
+        <is>
+          <t>Cu + B2O3 + 0.5 O2 -&gt; CuB2O4</t>
+        </is>
+      </c>
+      <c r="E19" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="49" t="inlineStr">
-        <is>
-          <t>NiO</t>
-        </is>
-      </c>
-      <c r="G16" s="50" t="n">
+      <c r="F19" s="35" t="inlineStr">
+        <is>
+          <t>B2O3</t>
+        </is>
+      </c>
+      <c r="G19" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" s="50" t="n">
+      <c r="H19" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" s="36" t="n">
         <v>0.5</v>
       </c>
-      <c r="J16" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="L16" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M16" s="51" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="52" t="inlineStr">
-        <is>
-          <t>CuLaO2</t>
-        </is>
-      </c>
-      <c r="B17" s="53" t="inlineStr">
-        <is>
-          <t>Copper lanthanum oxide</t>
-        </is>
-      </c>
-      <c r="C17" s="53" t="inlineStr">
-        <is>
-          <t>Compound</t>
-        </is>
-      </c>
-      <c r="D17" s="53" t="inlineStr">
-        <is>
-          <t>Cu + 0.5 La2O3 + 0.25 O2 -&gt; CuLaO2</t>
-        </is>
-      </c>
-      <c r="E17" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="53" t="inlineStr">
-        <is>
-          <t>La2O3</t>
-        </is>
-      </c>
-      <c r="G17" s="54" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H17" s="54" t="n">
-        <v>5</v>
-      </c>
-      <c r="I17" s="54" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J17" s="54" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K17" s="54" t="n">
-        <v>4</v>
-      </c>
-      <c r="L17" s="54" t="n">
-        <v>4</v>
-      </c>
-      <c r="M17" s="55" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="56" t="inlineStr">
-        <is>
-          <t>CuCeO3</t>
-        </is>
-      </c>
-      <c r="B18" s="57" t="inlineStr">
-        <is>
-          <t>Copper cerate (hyp.)</t>
-        </is>
-      </c>
-      <c r="C18" s="57" t="inlineStr">
-        <is>
-          <t>Hypothetical</t>
-        </is>
-      </c>
-      <c r="D18" s="57" t="inlineStr">
-        <is>
-          <t>Cu + CeO2 + 0.5 O2 -&gt; CuCeO3</t>
-        </is>
-      </c>
-      <c r="E18" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="57" t="inlineStr">
-        <is>
-          <t>CeO2</t>
-        </is>
-      </c>
-      <c r="G18" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="58" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" s="58" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J18" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" s="58" t="n">
-        <v>5</v>
-      </c>
-      <c r="L18" s="58" t="n">
-        <v>5</v>
-      </c>
-      <c r="M18" s="59" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="39" t="inlineStr">
-        <is>
-          <t>CuB2O4</t>
-        </is>
-      </c>
-      <c r="B19" s="40" t="inlineStr">
-        <is>
-          <t>Copper borate</t>
-        </is>
-      </c>
-      <c r="C19" s="40" t="inlineStr">
-        <is>
-          <t>Borate</t>
-        </is>
-      </c>
-      <c r="D19" s="40" t="inlineStr">
-        <is>
-          <t>Cu + B2O3 + 0.5 O2 -&gt; CuB2O4</t>
-        </is>
-      </c>
-      <c r="E19" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="40" t="inlineStr">
-        <is>
-          <t>B2O3</t>
-        </is>
-      </c>
-      <c r="G19" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="41" t="n">
-        <v>5</v>
-      </c>
-      <c r="I19" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J19" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" s="41" t="n">
+      <c r="J19" s="36">
+        <f>I19*2</f>
+        <v/>
+      </c>
+      <c r="K19" s="36">
+        <f>E19+G19*H19+J19</f>
+        <v/>
+      </c>
+      <c r="L19" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="L19" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="M19" s="42" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="M19" s="37">
+        <f>IF(ABS(K19-L19)&lt;0.01,"YES","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Notes:</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>All reactions require oxygen. In steelmaking, O2 comes from dissolved oxygen or atmosphere.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>n(oxide) = moles of binary oxide consumed per mole of ternary product.</t>
+          <t>All reactions require oxygen. In steelmaking, O2 comes from dissolved oxygen or atmosphere.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>Oxide Atoms = atoms per formula unit (e.g., Al2O3 = 5).</t>
+          <t>FORMULA CELLS: Cols J (O from O2), K (total atoms), M (balanced check) are Excel formulas.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>Total Reactant Atoms must equal Product Atoms for balanced reaction.</t>
+          <t>Total formula cells: 54.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
+          <t>n(oxide) = moles of binary oxide consumed per mole of ternary product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Oxide Atoms = atoms per formula unit (e.g., Al2O3 = 5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>Total Reactant Atoms must equal Product Atoms for balanced reaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
           <t>Hypothetical compounds have no known crystal structure; TC-Python determines stability.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="M2:M19">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
+      <formula>"YES"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
+      <formula>"NO"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4787,21 +5027,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1" ht="50" customHeight="1">
+    <row r="1" ht="55" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Product</t>
@@ -4838,18 +5088,80 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
+          <t>Prod
+Atoms</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>n_Cu</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>n_oxide</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Oxide
+Atoms</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>n_O₂</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>GM_product
+@ 1800K
+(J/mol-at)</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>G_Cu
+@ 1800K
+(J/mol)</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>GM_oxide
+@ 1800K
+(J/mol-at)</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>G_O₂
+@ 1800K
+(J/mol)</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
           <t>dG_rxn
 @ 1527C
-(kJ)</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
+(kJ) FORMULA</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>dG_rxn
+@ 1527C
+(kJ) CSV</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Ternary Phase
 @ 1527C</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Stable Phases
 @ 1527C</t>
@@ -4857,164 +5169,288 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="32" t="inlineStr">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>CuAl2O4</t>
         </is>
       </c>
-      <c r="B2" s="36" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>Copper aluminate spinel</t>
         </is>
       </c>
-      <c r="C2" s="33" t="inlineStr">
+      <c r="C2" s="29" t="inlineStr">
         <is>
           <t>Al2O3</t>
         </is>
       </c>
-      <c r="D2" s="36" t="inlineStr">
+      <c r="D2" s="32" t="inlineStr">
         <is>
           <t>Cu + Al2O3 + 0.5 O2 -&gt; CuAl2O4</t>
         </is>
       </c>
-      <c r="E2" s="60" t="n">
+      <c r="E2" s="54" t="n">
         <v>-72.7</v>
       </c>
-      <c r="F2" s="60" t="n">
+      <c r="F2" s="54" t="n">
         <v>-38.8</v>
       </c>
-      <c r="G2" s="60" t="n">
+      <c r="G2" s="55" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" s="55" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L2" s="56" t="n">
+        <v>-330029.0581573521</v>
+      </c>
+      <c r="M2" s="56" t="n">
+        <v>-110460.5952933756</v>
+      </c>
+      <c r="N2" s="56" t="n">
+        <v>-391060.1072913086</v>
+      </c>
+      <c r="O2" s="56" t="n">
+        <v>-424772.0805032522</v>
+      </c>
+      <c r="P2" s="57">
+        <f>(L2*G2-(H2*M2+I2*J2*N2+K2*O2))/1000</f>
+        <v/>
+      </c>
+      <c r="Q2" s="58" t="n">
         <v>-32.3</v>
       </c>
-      <c r="H2" s="36" t="inlineStr">
+      <c r="R2" s="32" t="inlineStr">
         <is>
           <t>SPINEL#1 (Stable up to 1550K (1277C))</t>
         </is>
       </c>
-      <c r="I2" s="37" t="inlineStr">
+      <c r="S2" s="33" t="inlineStr">
         <is>
           <t>CORUNDUM#1; GAS#1; IONIC_LIQ#2</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>CuAlO2</t>
         </is>
       </c>
-      <c r="B3" s="40" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>Delafossite</t>
         </is>
       </c>
-      <c r="C3" s="41" t="inlineStr">
+      <c r="C3" s="36" t="inlineStr">
         <is>
           <t>Al2O3</t>
         </is>
       </c>
-      <c r="D3" s="40" t="inlineStr">
+      <c r="D3" s="35" t="inlineStr">
         <is>
           <t>Cu + 0.5 Al2O3 + 0.25 O2 -&gt; CuAlO2</t>
         </is>
       </c>
-      <c r="E3" s="61" t="n">
+      <c r="E3" s="59" t="n">
         <v>-52.5</v>
       </c>
-      <c r="F3" s="61" t="n">
+      <c r="F3" s="59" t="n">
         <v>-35</v>
       </c>
-      <c r="G3" s="61" t="n">
+      <c r="G3" s="60" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="60" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J3" s="60" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" s="60" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L3" s="61" t="n">
+        <v>-306068.434453067</v>
+      </c>
+      <c r="M3" s="61" t="n">
+        <v>-110460.5952933756</v>
+      </c>
+      <c r="N3" s="61" t="n">
+        <v>-391060.1072913086</v>
+      </c>
+      <c r="O3" s="61" t="n">
+        <v>-424772.0805032522</v>
+      </c>
+      <c r="P3" s="62">
+        <f>(L3*G3-(H3*M3+I3*J3*N3+K3*O3))/1000</f>
+        <v/>
+      </c>
+      <c r="Q3" s="63" t="n">
         <v>-30.1</v>
       </c>
-      <c r="H3" s="40" t="inlineStr">
+      <c r="R3" s="35" t="inlineStr">
         <is>
           <t>DELAFOSSITE#1 (Stable up to 1550K (1277C))</t>
         </is>
       </c>
-      <c r="I3" s="62" t="inlineStr">
+      <c r="S3" s="64" t="inlineStr">
         <is>
           <t>CORUNDUM#1; IONIC_LIQ#1; IONIC_LIQ#2</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>CuCr2O4</t>
         </is>
       </c>
-      <c r="B4" s="44" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>Copper chromite spinel</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="40" t="inlineStr">
         <is>
           <t>Cr2O3</t>
         </is>
       </c>
-      <c r="D4" s="44" t="inlineStr">
+      <c r="D4" s="39" t="inlineStr">
         <is>
           <t>Cu + Cr2O3 + 0.5 O2 -&gt; CuCr2O4</t>
         </is>
       </c>
-      <c r="E4" s="63" t="n">
+      <c r="E4" s="65" t="n">
         <v>-82.3</v>
       </c>
-      <c r="F4" s="63" t="n">
+      <c r="F4" s="65" t="n">
         <v>-43.7</v>
       </c>
-      <c r="G4" s="63" t="n">
+      <c r="G4" s="66" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="66" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" s="66" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L4" s="67" t="n">
+        <v>-262147.7620709376</v>
+      </c>
+      <c r="M4" s="67" t="n">
+        <v>-110460.5952933756</v>
+      </c>
+      <c r="N4" s="67" t="n">
+        <v>-296471.243515468</v>
+      </c>
+      <c r="O4" s="67" t="n">
+        <v>-424772.0805032522</v>
+      </c>
+      <c r="P4" s="68">
+        <f>(L4*G4-(H4*M4+I4*J4*N4+K4*O4))/1000</f>
+        <v/>
+      </c>
+      <c r="Q4" s="69" t="n">
         <v>-30</v>
       </c>
-      <c r="H4" s="44" t="inlineStr">
+      <c r="R4" s="39" t="inlineStr">
         <is>
           <t>SPINEL#1 (Stable up to 1450K (1177C))</t>
         </is>
       </c>
-      <c r="I4" s="64" t="inlineStr">
+      <c r="S4" s="70" t="inlineStr">
         <is>
           <t>CORUNDUM#1; DELAFOSSITE#1; GAS#1</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>CuMn2O4</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Copper manganite spinel</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>MnO</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>Cu + 2MnO + O2 -&gt; CuMn2O4</t>
         </is>
       </c>
-      <c r="E5" s="65" t="n">
+      <c r="E5" s="71" t="n">
         <v>-161.8</v>
       </c>
-      <c r="F5" s="65" t="n">
+      <c r="F5" s="71" t="n">
         <v>-79.2</v>
       </c>
-      <c r="G5" s="65" t="n">
+      <c r="G5" s="72" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="73" t="n">
+        <v>-251354.9915712239</v>
+      </c>
+      <c r="M5" s="73" t="n">
+        <v>-110460.5952933756</v>
+      </c>
+      <c r="N5" s="73" t="n">
+        <v>-289951.205534343</v>
+      </c>
+      <c r="O5" s="73" t="n">
+        <v>-424772.0805032522</v>
+      </c>
+      <c r="P5" s="74">
+        <f>(L5*G5-(H5*M5+I5*J5*N5+K5*O5))/1000</f>
+        <v/>
+      </c>
+      <c r="Q5" s="75" t="n">
         <v>-64.40000000000001</v>
       </c>
-      <c r="H5" s="26" t="inlineStr">
+      <c r="R5" s="24" t="inlineStr">
         <is>
           <t>SPINEL#1 (Stable up to 1700K (1427C))</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="S5" s="25" t="inlineStr">
         <is>
           <t>GAS#1; IONIC_LIQ#2</t>
         </is>
@@ -5026,7 +5462,7 @@
           <t>CuFe2O4</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Copper ferrite spinel</t>
         </is>
@@ -5036,313 +5472,561 @@
           <t>FeO</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>Cu + 2FeO + O2 -&gt; CuFe2O4</t>
         </is>
       </c>
-      <c r="E6" s="65" t="n">
+      <c r="E6" s="76" t="n">
         <v>-235.7</v>
       </c>
-      <c r="F6" s="65" t="n">
+      <c r="F6" s="76" t="n">
         <v>-149.6</v>
       </c>
-      <c r="G6" s="65" t="n">
+      <c r="G6" s="77" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="78" t="n">
+        <v>-226811.1911823935</v>
+      </c>
+      <c r="M6" s="78" t="n">
+        <v>-110460.5952933756</v>
+      </c>
+      <c r="N6" s="78" t="n">
+        <v>-235131.7350722072</v>
+      </c>
+      <c r="O6" s="78" t="n">
+        <v>-424772.0805032522</v>
+      </c>
+      <c r="P6" s="79">
+        <f>(L6*G6-(H6*M6+I6*J6*N6+K6*O6))/1000</f>
+        <v/>
+      </c>
+      <c r="Q6" s="80" t="n">
         <v>-111.9</v>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="R6" s="19" t="inlineStr">
         <is>
           <t>SPINEL#1 (Stable up to 1700K (1427C))</t>
         </is>
       </c>
-      <c r="I6" s="21" t="inlineStr">
+      <c r="S6" s="20" t="inlineStr">
         <is>
           <t>GAS#1; IONIC_LIQ#2</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="52" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>CuCo2O4</t>
         </is>
       </c>
-      <c r="B7" s="53" t="inlineStr">
+      <c r="B7" s="47" t="inlineStr">
         <is>
           <t>Copper cobaltite spinel</t>
         </is>
       </c>
-      <c r="C7" s="54" t="inlineStr">
+      <c r="C7" s="48" t="inlineStr">
         <is>
           <t>CoO</t>
         </is>
       </c>
-      <c r="D7" s="53" t="inlineStr">
+      <c r="D7" s="47" t="inlineStr">
         <is>
           <t>Cu + 2CoO + O2 -&gt; CuCo2O4</t>
         </is>
       </c>
-      <c r="E7" s="60" t="n">
+      <c r="E7" s="81" t="n">
         <v>-91.40000000000001</v>
       </c>
-      <c r="F7" s="60" t="n">
+      <c r="F7" s="81" t="n">
         <v>-40.8</v>
       </c>
-      <c r="G7" s="60" t="n">
+      <c r="G7" s="82" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="82" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="82" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="83" t="n">
+        <v>-203900.5722657952</v>
+      </c>
+      <c r="M7" s="83" t="n">
+        <v>-110460.5952933756</v>
+      </c>
+      <c r="N7" s="83" t="n">
+        <v>-214067.5709469352</v>
+      </c>
+      <c r="O7" s="83" t="n">
+        <v>-424772.0805032522</v>
+      </c>
+      <c r="P7" s="84">
+        <f>(L7*G7-(H7*M7+I7*J7*N7+K7*O7))/1000</f>
+        <v/>
+      </c>
+      <c r="Q7" s="85" t="n">
         <v>-35.8</v>
       </c>
-      <c r="H7" s="53" t="inlineStr">
+      <c r="R7" s="47" t="inlineStr">
         <is>
           <t>SPINEL#1 (Stable up to 1150K (877C))</t>
         </is>
       </c>
-      <c r="I7" s="66" t="inlineStr">
+      <c r="S7" s="86" t="inlineStr">
         <is>
           <t>GAS#1; HALITE#1; IONIC_LIQ#2</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>CuV2O6</t>
         </is>
       </c>
-      <c r="B8" s="44" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>Copper vanadate</t>
         </is>
       </c>
-      <c r="C8" s="45" t="inlineStr">
+      <c r="C8" s="40" t="inlineStr">
         <is>
           <t>V2O5</t>
         </is>
       </c>
-      <c r="D8" s="44" t="inlineStr">
+      <c r="D8" s="39" t="inlineStr">
         <is>
           <t>Cu + V2O5 + 0.5 O2 -&gt; CuV2O6</t>
         </is>
       </c>
-      <c r="E8" s="63" t="n">
+      <c r="E8" s="65" t="n">
         <v>-66.7</v>
       </c>
-      <c r="F8" s="63" t="n">
+      <c r="F8" s="65" t="n">
         <v>-49.5</v>
       </c>
-      <c r="G8" s="63" t="n">
+      <c r="G8" s="66" t="n">
+        <v>9</v>
+      </c>
+      <c r="H8" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="66" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" s="66" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L8" s="67" t="n">
+        <v>-278155.0248504493</v>
+      </c>
+      <c r="M8" s="67" t="n">
+        <v>-110460.5952933756</v>
+      </c>
+      <c r="N8" s="67" t="n">
+        <v>-305109.3196037025</v>
+      </c>
+      <c r="O8" s="67" t="n">
+        <v>-424772.0805032522</v>
+      </c>
+      <c r="P8" s="68">
+        <f>(L8*G8-(H8*M8+I8*J8*N8+K8*O8))/1000</f>
+        <v/>
+      </c>
+      <c r="Q8" s="69" t="n">
         <v>-45</v>
       </c>
-      <c r="H8" s="44" t="inlineStr">
+      <c r="R8" s="39" t="inlineStr">
         <is>
           <t>Dissolved in ionic liquid</t>
         </is>
       </c>
-      <c r="I8" s="64" t="inlineStr">
+      <c r="S8" s="70" t="inlineStr">
         <is>
           <t>GAS#1; IONIC_LIQ#2</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="52" t="inlineStr">
+      <c r="A9" s="46" t="inlineStr">
         <is>
           <t>Cu3V2O8</t>
         </is>
       </c>
-      <c r="B9" s="53" t="inlineStr">
+      <c r="B9" s="47" t="inlineStr">
         <is>
           <t>Copper orthovanadate</t>
         </is>
       </c>
-      <c r="C9" s="54" t="inlineStr">
+      <c r="C9" s="48" t="inlineStr">
         <is>
           <t>V2O5</t>
         </is>
       </c>
-      <c r="D9" s="53" t="inlineStr">
+      <c r="D9" s="47" t="inlineStr">
         <is>
           <t>3Cu + V2O5 + 1.5 O2 -&gt; Cu3V2O8</t>
         </is>
       </c>
-      <c r="E9" s="60" t="n">
+      <c r="E9" s="81" t="n">
         <v>-198.7</v>
       </c>
-      <c r="F9" s="60" t="n">
+      <c r="F9" s="81" t="n">
         <v>-127.1</v>
       </c>
-      <c r="G9" s="60" t="n">
+      <c r="G9" s="82" t="n">
+        <v>13</v>
+      </c>
+      <c r="H9" s="82" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="82" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" s="82" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L9" s="83" t="n">
+        <v>-247173.7118812478</v>
+      </c>
+      <c r="M9" s="83" t="n">
+        <v>-110460.5952933756</v>
+      </c>
+      <c r="N9" s="83" t="n">
+        <v>-305109.3196037025</v>
+      </c>
+      <c r="O9" s="83" t="n">
+        <v>-424772.0805032522</v>
+      </c>
+      <c r="P9" s="84">
+        <f>(L9*G9-(H9*M9+I9*J9*N9+K9*O9))/1000</f>
+        <v/>
+      </c>
+      <c r="Q9" s="85" t="n">
         <v>-109.2</v>
       </c>
-      <c r="H9" s="53" t="inlineStr">
+      <c r="R9" s="47" t="inlineStr">
         <is>
           <t>Dissolved in ionic liquid</t>
         </is>
       </c>
-      <c r="I9" s="66" t="inlineStr">
+      <c r="S9" s="86" t="inlineStr">
         <is>
           <t>GAS#1; IONIC_LIQ#2</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="56" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t>CuTiO3</t>
         </is>
       </c>
-      <c r="B10" s="57" t="inlineStr">
+      <c r="B10" s="51" t="inlineStr">
         <is>
           <t>Copper titanate</t>
         </is>
       </c>
-      <c r="C10" s="58" t="inlineStr">
+      <c r="C10" s="52" t="inlineStr">
         <is>
           <t>TiO2</t>
         </is>
       </c>
-      <c r="D10" s="57" t="inlineStr">
+      <c r="D10" s="51" t="inlineStr">
         <is>
           <t>Cu + TiO2 + 0.5 O2 -&gt; CuTiO3</t>
         </is>
       </c>
-      <c r="E10" s="61" t="n">
+      <c r="E10" s="87" t="n">
         <v>-66.2</v>
       </c>
-      <c r="F10" s="61" t="n">
+      <c r="F10" s="87" t="n">
         <v>-37.3</v>
       </c>
-      <c r="G10" s="61" t="n">
+      <c r="G10" s="88" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" s="88" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="88" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="88" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" s="88" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L10" s="89" t="n">
+        <v>-302140.2488485489</v>
+      </c>
+      <c r="M10" s="89" t="n">
+        <v>-110460.5952933756</v>
+      </c>
+      <c r="N10" s="89" t="n">
+        <v>-383573.9712871907</v>
+      </c>
+      <c r="O10" s="89" t="n">
+        <v>-424772.0805032522</v>
+      </c>
+      <c r="P10" s="90">
+        <f>(L10*G10-(H10*M10+I10*J10*N10+K10*O10))/1000</f>
+        <v/>
+      </c>
+      <c r="Q10" s="91" t="n">
         <v>-36.8</v>
       </c>
-      <c r="H10" s="57" t="inlineStr">
+      <c r="R10" s="51" t="inlineStr">
         <is>
           <t>Dissolved in ionic liquid</t>
         </is>
       </c>
-      <c r="I10" s="67" t="inlineStr">
+      <c r="S10" s="92" t="inlineStr">
         <is>
           <t>GAS#1; IONIC_LIQ#2</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="48" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>CuSiO3</t>
         </is>
       </c>
-      <c r="B11" s="49" t="inlineStr">
+      <c r="B11" s="43" t="inlineStr">
         <is>
           <t>Copper metasilicate</t>
         </is>
       </c>
-      <c r="C11" s="50" t="inlineStr">
+      <c r="C11" s="44" t="inlineStr">
         <is>
           <t>SiO2</t>
         </is>
       </c>
-      <c r="D11" s="49" t="inlineStr">
+      <c r="D11" s="43" t="inlineStr">
         <is>
           <t>Cu + SiO2 + 0.5 O2 -&gt; CuSiO3</t>
         </is>
       </c>
-      <c r="E11" s="63" t="n">
+      <c r="E11" s="93" t="n">
         <v>-66.2</v>
       </c>
-      <c r="F11" s="63" t="n">
+      <c r="F11" s="93" t="n">
         <v>-32.9</v>
       </c>
-      <c r="G11" s="63" t="n">
+      <c r="G11" s="94" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="94" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" s="94" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L11" s="95" t="n">
+        <v>-288510.8415733827</v>
+      </c>
+      <c r="M11" s="95" t="n">
+        <v>-110460.5952933756</v>
+      </c>
+      <c r="N11" s="95" t="n">
+        <v>-364407.9370427133</v>
+      </c>
+      <c r="O11" s="95" t="n">
+        <v>-424772.0805032522</v>
+      </c>
+      <c r="P11" s="96">
+        <f>(L11*G11-(H11*M11+I11*J11*N11+K11*O11))/1000</f>
+        <v/>
+      </c>
+      <c r="Q11" s="97" t="n">
         <v>-26.2</v>
       </c>
-      <c r="H11" s="49" t="inlineStr">
+      <c r="R11" s="43" t="inlineStr">
         <is>
           <t>Dissolved in ionic liquid</t>
         </is>
       </c>
-      <c r="I11" s="68" t="inlineStr">
+      <c r="S11" s="98" t="inlineStr">
         <is>
           <t>CRISTOBALITE#1; GAS#1; IONIC_LIQ#2</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>Cu2SiO4</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>Copper orthosilicate</t>
         </is>
       </c>
-      <c r="C12" s="33" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>SiO2</t>
         </is>
       </c>
-      <c r="D12" s="36" t="inlineStr">
+      <c r="D12" s="32" t="inlineStr">
         <is>
           <t>2Cu + SiO2 + O2 -&gt; Cu2SiO4</t>
         </is>
       </c>
-      <c r="E12" s="60" t="n">
+      <c r="E12" s="54" t="n">
         <v>-132.2</v>
       </c>
-      <c r="F12" s="60" t="n">
+      <c r="F12" s="54" t="n">
         <v>-65.7</v>
       </c>
-      <c r="G12" s="60" t="n">
+      <c r="G12" s="55" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="55" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="56" t="n">
+        <v>-255918.2974852123</v>
+      </c>
+      <c r="M12" s="56" t="n">
+        <v>-110460.5952933756</v>
+      </c>
+      <c r="N12" s="56" t="n">
+        <v>-364407.9370427133</v>
+      </c>
+      <c r="O12" s="56" t="n">
+        <v>-424772.0805032522</v>
+      </c>
+      <c r="P12" s="57">
+        <f>(L12*G12-(H12*M12+I12*J12*N12+K12*O12))/1000</f>
+        <v/>
+      </c>
+      <c r="Q12" s="58" t="n">
         <v>-52.2</v>
       </c>
-      <c r="H12" s="36" t="inlineStr">
+      <c r="R12" s="32" t="inlineStr">
         <is>
           <t>Dissolved in ionic liquid</t>
         </is>
       </c>
-      <c r="I12" s="37" t="inlineStr">
+      <c r="S12" s="33" t="inlineStr">
         <is>
           <t>CRISTOBALITE#1; GAS#1; IONIC_LIQ#2</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="48" t="inlineStr">
+      <c r="A13" s="42" t="inlineStr">
         <is>
           <t>CuMgO2</t>
         </is>
       </c>
-      <c r="B13" s="49" t="inlineStr">
+      <c r="B13" s="43" t="inlineStr">
         <is>
           <t>Copper magnesioxide (hyp.)</t>
         </is>
       </c>
-      <c r="C13" s="50" t="inlineStr">
+      <c r="C13" s="44" t="inlineStr">
         <is>
           <t>MgO</t>
         </is>
       </c>
-      <c r="D13" s="49" t="inlineStr">
+      <c r="D13" s="43" t="inlineStr">
         <is>
           <t>Cu + MgO + 0.5 O2 -&gt; CuMgO2</t>
         </is>
       </c>
-      <c r="E13" s="63" t="n">
+      <c r="E13" s="93" t="n">
         <v>-67.90000000000001</v>
       </c>
-      <c r="F13" s="63" t="n">
+      <c r="F13" s="93" t="n">
         <v>-33.9</v>
       </c>
-      <c r="G13" s="63" t="n">
+      <c r="G13" s="94" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="94" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" s="94" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L13" s="95" t="n">
+        <v>-269776.9427837598</v>
+      </c>
+      <c r="M13" s="95" t="n">
+        <v>-110460.5952933756</v>
+      </c>
+      <c r="N13" s="95" t="n">
+        <v>-365091.5399254378</v>
+      </c>
+      <c r="O13" s="95" t="n">
+        <v>-424772.0805032522</v>
+      </c>
+      <c r="P13" s="96">
+        <f>(L13*G13-(H13*M13+I13*J13*N13+K13*O13))/1000</f>
+        <v/>
+      </c>
+      <c r="Q13" s="97" t="n">
         <v>-26.1</v>
       </c>
-      <c r="H13" s="49" t="inlineStr">
+      <c r="R13" s="43" t="inlineStr">
         <is>
           <t>Dissolved in ionic liquid</t>
         </is>
       </c>
-      <c r="I13" s="68" t="inlineStr">
+      <c r="S13" s="98" t="inlineStr">
         <is>
           <t>GAS#1; HALITE#1; IONIC_LIQ#2</t>
         </is>
@@ -5354,7 +6038,7 @@
           <t>CuCaO2</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>Copper calcioxide (hyp.)</t>
         </is>
@@ -5364,292 +6048,540 @@
           <t>CaO</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>Cu + CaO + 0.5 O2 -&gt; CuCaO2</t>
         </is>
       </c>
-      <c r="E14" s="65" t="n">
+      <c r="E14" s="76" t="n">
         <v>-67.3</v>
       </c>
-      <c r="F14" s="65" t="n">
+      <c r="F14" s="76" t="n">
         <v>-36.6</v>
       </c>
-      <c r="G14" s="65" t="n">
+      <c r="G14" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L14" s="78" t="n">
+        <v>-285774.276838706</v>
+      </c>
+      <c r="M14" s="78" t="n">
+        <v>-110460.5952933756</v>
+      </c>
+      <c r="N14" s="78" t="n">
+        <v>-394797.2636177477</v>
+      </c>
+      <c r="O14" s="78" t="n">
+        <v>-424772.0805032522</v>
+      </c>
+      <c r="P14" s="79">
+        <f>(L14*G14-(H14*M14+I14*J14*N14+K14*O14))/1000</f>
+        <v/>
+      </c>
+      <c r="Q14" s="80" t="n">
         <v>-30.7</v>
       </c>
-      <c r="H14" s="20" t="inlineStr">
+      <c r="R14" s="19" t="inlineStr">
         <is>
           <t>Dissolved in ionic liquid</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
+      <c r="S14" s="20" t="inlineStr">
         <is>
           <t>GAS#1; HALITE#1; IONIC_LIQ#2</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="52" t="inlineStr">
+      <c r="A15" s="46" t="inlineStr">
         <is>
           <t>CuZrO3</t>
         </is>
       </c>
-      <c r="B15" s="53" t="inlineStr">
+      <c r="B15" s="47" t="inlineStr">
         <is>
           <t>Copper zirconate (hyp.)</t>
         </is>
       </c>
-      <c r="C15" s="54" t="inlineStr">
+      <c r="C15" s="48" t="inlineStr">
         <is>
           <t>ZrO2</t>
         </is>
       </c>
-      <c r="D15" s="53" t="inlineStr">
+      <c r="D15" s="47" t="inlineStr">
         <is>
           <t>Cu + ZrO2 + 0.5 O2 -&gt; CuZrO3</t>
         </is>
       </c>
-      <c r="E15" s="60" t="n">
+      <c r="E15" s="81" t="n">
         <v>-66.3</v>
       </c>
-      <c r="F15" s="60" t="n">
+      <c r="F15" s="81" t="n">
         <v>-32.2</v>
       </c>
-      <c r="G15" s="60" t="n">
+      <c r="G15" s="82" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="82" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" s="82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L15" s="83" t="n">
+        <v>-331801.7810053322</v>
+      </c>
+      <c r="M15" s="83" t="n">
+        <v>-110460.5952933756</v>
+      </c>
+      <c r="N15" s="83" t="n">
+        <v>-436797.3102753915</v>
+      </c>
+      <c r="O15" s="83" t="n">
+        <v>-424772.0805032522</v>
+      </c>
+      <c r="P15" s="84">
+        <f>(L15*G15-(H15*M15+I15*J15*N15+K15*O15))/1000</f>
+        <v/>
+      </c>
+      <c r="Q15" s="85" t="n">
         <v>-25.3</v>
       </c>
-      <c r="H15" s="53" t="inlineStr">
+      <c r="R15" s="47" t="inlineStr">
         <is>
           <t>Dissolved in ionic liquid</t>
         </is>
       </c>
-      <c r="I15" s="66" t="inlineStr">
+      <c r="S15" s="86" t="inlineStr">
         <is>
           <t>GAS#1; IONIC_LIQ#2; ZRO2_TETR#1</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="43" t="inlineStr">
+      <c r="A16" s="38" t="inlineStr">
         <is>
           <t>CuNiO2</t>
         </is>
       </c>
-      <c r="B16" s="44" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>Copper nickelate</t>
         </is>
       </c>
-      <c r="C16" s="45" t="inlineStr">
+      <c r="C16" s="40" t="inlineStr">
         <is>
           <t>NiO</t>
         </is>
       </c>
-      <c r="D16" s="44" t="inlineStr">
+      <c r="D16" s="39" t="inlineStr">
         <is>
           <t>Cu + NiO + 0.5 O2 -&gt; CuNiO2</t>
         </is>
       </c>
-      <c r="E16" s="63" t="n">
+      <c r="E16" s="65" t="n">
         <v>-70.59999999999999</v>
       </c>
-      <c r="F16" s="63" t="n">
+      <c r="F16" s="65" t="n">
         <v>-35.4</v>
       </c>
-      <c r="G16" s="63" t="n">
+      <c r="G16" s="66" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="66" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" s="66" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L16" s="67" t="n">
+        <v>-187971.6778645938</v>
+      </c>
+      <c r="M16" s="67" t="n">
+        <v>-110460.5952933756</v>
+      </c>
+      <c r="N16" s="67" t="n">
+        <v>-200848.0620923697</v>
+      </c>
+      <c r="O16" s="67" t="n">
+        <v>-424772.0805032522</v>
+      </c>
+      <c r="P16" s="68">
+        <f>(L16*G16-(H16*M16+I16*J16*N16+K16*O16))/1000</f>
+        <v/>
+      </c>
+      <c r="Q16" s="69" t="n">
         <v>-27.3</v>
       </c>
-      <c r="H16" s="44" t="inlineStr">
+      <c r="R16" s="39" t="inlineStr">
         <is>
           <t>Dissolved in ionic liquid</t>
         </is>
       </c>
-      <c r="I16" s="64" t="inlineStr">
+      <c r="S16" s="70" t="inlineStr">
         <is>
           <t>GAS#1; HALITE#1; IONIC_LIQ#2</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="52" t="inlineStr">
+      <c r="A17" s="46" t="inlineStr">
         <is>
           <t>CuLaO2</t>
         </is>
       </c>
-      <c r="B17" s="53" t="inlineStr">
+      <c r="B17" s="47" t="inlineStr">
         <is>
           <t>Copper lanthanum oxide</t>
         </is>
       </c>
-      <c r="C17" s="54" t="inlineStr">
+      <c r="C17" s="48" t="inlineStr">
         <is>
           <t>La2O3</t>
         </is>
       </c>
-      <c r="D17" s="53" t="inlineStr">
+      <c r="D17" s="47" t="inlineStr">
         <is>
           <t>Cu + 0.5 La2O3 + 0.25 O2 -&gt; CuLaO2</t>
         </is>
       </c>
-      <c r="E17" s="60" t="n">
+      <c r="E17" s="81" t="n">
         <v>-50.9</v>
       </c>
-      <c r="F17" s="60" t="n">
+      <c r="F17" s="81" t="n">
         <v>-31.1</v>
       </c>
-      <c r="G17" s="60" t="n">
+      <c r="G17" s="82" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J17" s="82" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" s="82" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L17" s="83" t="n">
+        <v>-340569.7762879045</v>
+      </c>
+      <c r="M17" s="83" t="n">
+        <v>-110460.5952933756</v>
+      </c>
+      <c r="N17" s="83" t="n">
+        <v>-447180.6182450477</v>
+      </c>
+      <c r="O17" s="83" t="n">
+        <v>-424772.0805032522</v>
+      </c>
+      <c r="P17" s="84">
+        <f>(L17*G17-(H17*M17+I17*J17*N17+K17*O17))/1000</f>
+        <v/>
+      </c>
+      <c r="Q17" s="85" t="n">
         <v>-27.8</v>
       </c>
-      <c r="H17" s="53" t="inlineStr">
+      <c r="R17" s="47" t="inlineStr">
         <is>
           <t>DELAFOSSITE#1 (Stable up to 1500K (1227C))</t>
         </is>
       </c>
-      <c r="I17" s="66" t="inlineStr">
+      <c r="S17" s="86" t="inlineStr">
         <is>
           <t>IONIC_LIQ#1; IONIC_LIQ#2; M2O3A#1</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="56" t="inlineStr">
+      <c r="A18" s="50" t="inlineStr">
         <is>
           <t>CuCeO3</t>
         </is>
       </c>
-      <c r="B18" s="57" t="inlineStr">
+      <c r="B18" s="51" t="inlineStr">
         <is>
           <t>Copper cerate (hyp.)</t>
         </is>
       </c>
-      <c r="C18" s="58" t="inlineStr">
+      <c r="C18" s="52" t="inlineStr">
         <is>
           <t>CeO2</t>
         </is>
       </c>
-      <c r="D18" s="57" t="inlineStr">
+      <c r="D18" s="51" t="inlineStr">
         <is>
           <t>Cu + CeO2 + 0.5 O2 -&gt; CuCeO3</t>
         </is>
       </c>
-      <c r="E18" s="69" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="F18" s="69" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="G18" s="69" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="H18" s="57" t="inlineStr">
+      <c r="E18" s="99" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F18" s="99" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G18" s="88" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" s="88" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="88" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="88" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" s="88" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L18" s="99" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="M18" s="99" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="N18" s="99" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="O18" s="99" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="P18" s="99" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="Q18" s="99" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="R18" s="51" t="inlineStr">
         <is>
           <t>Dissolved in ionic liquid</t>
         </is>
       </c>
-      <c r="I18" s="67" t="inlineStr">
+      <c r="S18" s="92" t="inlineStr">
         <is>
           <t>ERROR: Thermo-Calc calculation error: se.thermocalc.core.CalculationEngineException: The element CE is not in the database, it contains only the following elements: [/-, AL, AR, B, BA, C, CA, CO, CR, CU, F, FE, GD, H, HF, K, LA, LI, MG, MN, MO, N, NA, NB, NI, O, P, S, SI, TI, V, VA, W, Y, YB, ZR]</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="39" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>CuB2O4</t>
         </is>
       </c>
-      <c r="B19" s="40" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>Copper borate</t>
         </is>
       </c>
-      <c r="C19" s="41" t="inlineStr">
+      <c r="C19" s="36" t="inlineStr">
         <is>
           <t>B2O3</t>
         </is>
       </c>
-      <c r="D19" s="40" t="inlineStr">
+      <c r="D19" s="35" t="inlineStr">
         <is>
           <t>Cu + B2O3 + 0.5 O2 -&gt; CuB2O4</t>
         </is>
       </c>
-      <c r="E19" s="61" t="n">
+      <c r="E19" s="59" t="n">
         <v>-79.7</v>
       </c>
-      <c r="F19" s="61" t="n">
+      <c r="F19" s="59" t="n">
         <v>-51.3</v>
       </c>
-      <c r="G19" s="61" t="n">
+      <c r="G19" s="60" t="n">
+        <v>7</v>
+      </c>
+      <c r="H19" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="60" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" s="60" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L19" s="61" t="n">
+        <v>-278569.2410931564</v>
+      </c>
+      <c r="M19" s="61" t="n">
+        <v>-110460.5952933756</v>
+      </c>
+      <c r="N19" s="61" t="n">
+        <v>-315909.8169720008</v>
+      </c>
+      <c r="O19" s="61" t="n">
+        <v>-424772.0805032522</v>
+      </c>
+      <c r="P19" s="62">
+        <f>(L19*G19-(H19*M19+I19*J19*N19+K19*O19))/1000</f>
+        <v/>
+      </c>
+      <c r="Q19" s="63" t="n">
         <v>-47.7</v>
       </c>
-      <c r="H19" s="40" t="inlineStr">
+      <c r="R19" s="35" t="inlineStr">
         <is>
           <t>Dissolved in ionic liquid</t>
         </is>
       </c>
-      <c r="I19" s="62" t="inlineStr">
+      <c r="S19" s="64" t="inlineStr">
         <is>
           <t>GAS#1; IONIC_LIQ#2</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Notes:</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>dG_rxn = G(products) - G(reactants)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>G(products) = GM_system(ternary composition) x atoms_per_formula</t>
+          <t>FORMULA COLUMN (P) computes dG from raw TC-Python values (L-O) and stoichiometry (G-K):</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>G(reactants) = n_Cu x G(Cu metal) + n_oxide x oxide_atoms x G(binary oxide) + n_O2 x G(O2 gas)</t>
+          <t xml:space="preserve">  dG_rxn = (GM_product × prod_atoms - (n_Cu × G_Cu + n_oxide × ox_atoms × GM_oxide + n_O₂ × G_O₂)) / 1000</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>Negative dG = FAVORABLE (oxide captures copper into ternary compound)</t>
+          <t>CSV COLUMN (Q) shows the same dG pre-computed by the Python extraction script — should match P exactly.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>Positive dG = UNFAVORABLE (ternary compound does not form spontaneously)</t>
+          <t>If P ≠ Q, the discrepancy is due to the binary oxide reference: P uses the binary CSV (Tab 1 source),</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">  while Q uses a binary oxide recalculated inside the ternary system (typically &lt;0.1% difference).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>Columns L-O are RAW values from TC-Python (TCOX14 database). No arithmetic applied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>Negative dG = FAVORABLE (oxide captures copper into ternary compound).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
           <t>Green cells = favorable.  Red = unfavorable.</t>
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Formula cells in this tab: 17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="P2:P19">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="2">
+      <formula>-10</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:Q19">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="2">
+      <formula>-10</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E19">
+    <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F19">
+    <cfRule type="cellIs" priority="7" operator="lessThan" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5660,7 +6592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5771,89 +6703,85 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F2" s="18" t="n">
-        <v>1240.711951535208</v>
-      </c>
-      <c r="G2" s="28" t="inlineStr">
-        <is>
-          <t>CANNOT reduce</t>
-        </is>
-      </c>
-      <c r="H2" s="20" t="inlineStr">
+      <c r="F2" s="18">
+        <f>'Binary Screening'!H2</f>
+        <v/>
+      </c>
+      <c r="G2" s="17">
+        <f>'Binary Screening'!I2</f>
+        <v/>
+      </c>
+      <c r="H2" s="19" t="inlineStr">
         <is>
           <t>CuCeO3</t>
         </is>
       </c>
-      <c r="I2" s="31" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="J2" s="17" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="K2" s="20" t="inlineStr">
-        <is>
-          <t>Awaiting ternary data</t>
-        </is>
-      </c>
-      <c r="L2" s="21" t="inlineStr">
+      <c r="I2" s="18">
+        <f>IFERROR('Ternary Reaction dG'!P18,"TBD")</f>
+        <v/>
+      </c>
+      <c r="J2" s="17">
+        <f>IF(NOT(ISNUMBER(I2)),"TBD",IF(I2&lt;-10,"FAVORABLE",IF(I2&lt;0,"Marginal",IF(I2&lt;10,"Borderline","Unfavorable"))))</f>
+        <v/>
+      </c>
+      <c r="K2" s="19">
+        <f>IF(NOT(ISNUMBER(I2)),"Awaiting ternary data",IF(I2&lt;-10,"PROMISING - ternary compound forms",IF(I2&lt;0,"Marginal - weak compound formation",IF(A2="CuO","Trivial - further Cu oxidation","Not promising at steelmaking temps"))))</f>
+        <v/>
+      </c>
+      <c r="L2" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>CaO</t>
         </is>
       </c>
-      <c r="B3" s="23" t="n">
+      <c r="B3" s="22" t="n">
         <v>3.34</v>
       </c>
-      <c r="C3" s="23" t="n">
+      <c r="C3" s="22" t="n">
         <v>2613</v>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E3" s="23" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F3" s="24" t="n">
-        <v>791.3091397887691</v>
-      </c>
-      <c r="G3" s="29" t="inlineStr">
-        <is>
-          <t>CANNOT reduce</t>
-        </is>
-      </c>
-      <c r="H3" s="26" t="inlineStr">
+      <c r="F3" s="23">
+        <f>'Binary Screening'!H3</f>
+        <v/>
+      </c>
+      <c r="G3" s="22">
+        <f>'Binary Screening'!I3</f>
+        <v/>
+      </c>
+      <c r="H3" s="24" t="inlineStr">
         <is>
           <t>CuCaO2</t>
         </is>
       </c>
-      <c r="I3" s="65" t="n">
-        <v>-30.73549587729294</v>
-      </c>
-      <c r="J3" s="70" t="inlineStr">
-        <is>
-          <t>FAVORABLE</t>
-        </is>
-      </c>
-      <c r="K3" s="71" t="inlineStr">
-        <is>
-          <t>PROMISING — ternary compound forms</t>
-        </is>
-      </c>
-      <c r="L3" s="27" t="inlineStr">
+      <c r="I3" s="23">
+        <f>IFERROR('Ternary Reaction dG'!P14,"TBD")</f>
+        <v/>
+      </c>
+      <c r="J3" s="22">
+        <f>IF(NOT(ISNUMBER(I3)),"TBD",IF(I3&lt;-10,"FAVORABLE",IF(I3&lt;0,"Marginal",IF(I3&lt;10,"Borderline","Unfavorable"))))</f>
+        <v/>
+      </c>
+      <c r="K3" s="24">
+        <f>IF(NOT(ISNUMBER(I3)),"Awaiting ternary data",IF(I3&lt;-10,"PROMISING - ternary compound forms",IF(I3&lt;0,"Marginal - weak compound formation",IF(A3="CuO","Trivial - further Cu oxidation","Not promising at steelmaking temps"))))</f>
+        <v/>
+      </c>
+      <c r="L3" s="25" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -5881,87 +6809,85 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F4" s="18" t="n">
-        <v>766.2790754363556</v>
-      </c>
-      <c r="G4" s="28" t="inlineStr">
-        <is>
-          <t>CANNOT reduce</t>
-        </is>
-      </c>
-      <c r="H4" s="20" t="inlineStr">
+      <c r="F4" s="18">
+        <f>'Binary Screening'!H4</f>
+        <v/>
+      </c>
+      <c r="G4" s="17">
+        <f>'Binary Screening'!I4</f>
+        <v/>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>CuLaO2</t>
         </is>
       </c>
-      <c r="I4" s="65" t="n">
-        <v>-27.83838194089453</v>
-      </c>
-      <c r="J4" s="72" t="inlineStr">
-        <is>
-          <t>FAVORABLE</t>
-        </is>
-      </c>
-      <c r="K4" s="71" t="inlineStr">
-        <is>
-          <t>PROMISING — ternary compound forms</t>
-        </is>
-      </c>
-      <c r="L4" s="21" t="inlineStr">
+      <c r="I4" s="18">
+        <f>IFERROR('Ternary Reaction dG'!P17,"TBD")</f>
+        <v/>
+      </c>
+      <c r="J4" s="17">
+        <f>IF(NOT(ISNUMBER(I4)),"TBD",IF(I4&lt;-10,"FAVORABLE",IF(I4&lt;0,"Marginal",IF(I4&lt;10,"Borderline","Unfavorable"))))</f>
+        <v/>
+      </c>
+      <c r="K4" s="19">
+        <f>IF(NOT(ISNUMBER(I4)),"Awaiting ternary data",IF(I4&lt;-10,"PROMISING - ternary compound forms",IF(I4&lt;0,"Marginal - weak compound formation",IF(A4="CuO","Trivial - further Cu oxidation","Not promising at steelmaking temps"))))</f>
+        <v/>
+      </c>
+      <c r="L4" s="20" t="inlineStr">
         <is>
           <t>Low-Moderate</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>MgO</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n">
+      <c r="B5" s="22" t="n">
         <v>3.58</v>
       </c>
-      <c r="C5" s="23" t="n">
+      <c r="C5" s="22" t="n">
         <v>2852</v>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F5" s="24" t="n">
-        <v>642.8620279630527</v>
-      </c>
-      <c r="G5" s="29" t="inlineStr">
-        <is>
-          <t>CANNOT reduce</t>
-        </is>
-      </c>
-      <c r="H5" s="26" t="inlineStr">
+      <c r="F5" s="23">
+        <f>'Binary Screening'!H5</f>
+        <v/>
+      </c>
+      <c r="G5" s="22">
+        <f>'Binary Screening'!I5</f>
+        <v/>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
         <is>
           <t>CuMgO2</t>
         </is>
       </c>
-      <c r="I5" s="65" t="n">
-        <v>-26.13572675267817</v>
-      </c>
-      <c r="J5" s="70" t="inlineStr">
-        <is>
-          <t>FAVORABLE</t>
-        </is>
-      </c>
-      <c r="K5" s="71" t="inlineStr">
-        <is>
-          <t>PROMISING — ternary compound forms</t>
-        </is>
-      </c>
-      <c r="L5" s="27" t="inlineStr">
+      <c r="I5" s="23">
+        <f>IFERROR('Ternary Reaction dG'!P13,"TBD")</f>
+        <v/>
+      </c>
+      <c r="J5" s="22">
+        <f>IF(NOT(ISNUMBER(I5)),"TBD",IF(I5&lt;-10,"FAVORABLE",IF(I5&lt;0,"Marginal",IF(I5&lt;10,"Borderline","Unfavorable"))))</f>
+        <v/>
+      </c>
+      <c r="K5" s="24">
+        <f>IF(NOT(ISNUMBER(I5)),"Awaiting ternary data",IF(I5&lt;-10,"PROMISING - ternary compound forms",IF(I5&lt;0,"Marginal - weak compound formation",IF(A5="CuO","Trivial - further Cu oxidation","Not promising at steelmaking temps"))))</f>
+        <v/>
+      </c>
+      <c r="L5" s="25" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -5989,87 +6915,84 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F6" s="18" t="n">
-        <v>675.6992805726175</v>
-      </c>
-      <c r="G6" s="28" t="inlineStr">
-        <is>
-          <t>CANNOT reduce</t>
-        </is>
-      </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="F6" s="18">
+        <f>'Binary Screening'!H6</f>
+        <v/>
+      </c>
+      <c r="G6" s="17">
+        <f>'Binary Screening'!I6</f>
+        <v/>
+      </c>
+      <c r="H6" s="19" t="inlineStr">
         <is>
           <t>CuZrO3</t>
         </is>
       </c>
-      <c r="I6" s="65" t="n">
-        <v>-25.3216517171904</v>
-      </c>
-      <c r="J6" s="72" t="inlineStr">
-        <is>
-          <t>FAVORABLE</t>
-        </is>
-      </c>
-      <c r="K6" s="71" t="inlineStr">
-        <is>
-          <t>PROMISING — ternary compound forms</t>
-        </is>
-      </c>
-      <c r="L6" s="21" t="inlineStr">
+      <c r="I6" s="18">
+        <f>IFERROR('Ternary Reaction dG'!P15,"TBD")</f>
+        <v/>
+      </c>
+      <c r="J6" s="17">
+        <f>IF(NOT(ISNUMBER(I6)),"TBD",IF(I6&lt;-10,"FAVORABLE",IF(I6&lt;0,"Marginal",IF(I6&lt;10,"Borderline","Unfavorable"))))</f>
+        <v/>
+      </c>
+      <c r="K6" s="19">
+        <f>IF(NOT(ISNUMBER(I6)),"Awaiting ternary data",IF(I6&lt;-10,"PROMISING - ternary compound forms",IF(I6&lt;0,"Marginal - weak compound formation",IF(A6="CuO","Trivial - further Cu oxidation","Not promising at steelmaking temps"))))</f>
+        <v/>
+      </c>
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Al2O3</t>
         </is>
       </c>
-      <c r="B7" s="23" t="n">
+      <c r="B7" s="22" t="n">
         <v>3.95</v>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C7" s="22" t="n">
         <v>2072</v>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F7" s="24" t="n">
-        <v>644.8222226505188</v>
-      </c>
-      <c r="G7" s="29" t="inlineStr">
-        <is>
-          <t>CANNOT reduce</t>
-        </is>
-      </c>
-      <c r="H7" s="26" t="inlineStr">
-        <is>
-          <t>CuAl2O4</t>
-        </is>
-      </c>
-      <c r="I7" s="65" t="n">
-        <v>-32.31451216300158</v>
-      </c>
-      <c r="J7" s="70" t="inlineStr">
-        <is>
-          <t>FAVORABLE</t>
-        </is>
-      </c>
-      <c r="K7" s="71" t="inlineStr">
-        <is>
-          <t>PROMISING — ternary compound forms</t>
-        </is>
-      </c>
-      <c r="L7" s="27" t="inlineStr">
+      <c r="F7" s="23">
+        <f>'Binary Screening'!H7</f>
+        <v/>
+      </c>
+      <c r="G7" s="22">
+        <f>'Binary Screening'!I7</f>
+        <v/>
+      </c>
+      <c r="H7" s="24">
+        <f>IFERROR(INDEX('Ternary Reaction dG'!A2:A3,MATCH(MIN('Ternary Reaction dG'!P2:G3),'Ternary Reaction dG'!P2:G3,0)),"N/A")</f>
+        <v/>
+      </c>
+      <c r="I7" s="23">
+        <f>IFERROR(MIN('Ternary Reaction dG'!P2:G3),"TBD")</f>
+        <v/>
+      </c>
+      <c r="J7" s="22">
+        <f>IF(NOT(ISNUMBER(I7)),"TBD",IF(I7&lt;-10,"FAVORABLE",IF(I7&lt;0,"Marginal",IF(I7&lt;10,"Borderline","Unfavorable"))))</f>
+        <v/>
+      </c>
+      <c r="K7" s="24">
+        <f>IF(NOT(ISNUMBER(I7)),"Awaiting ternary data",IF(I7&lt;-10,"PROMISING - ternary compound forms",IF(I7&lt;0,"Marginal - weak compound formation",IF(A7="CuO","Trivial - further Cu oxidation","Not promising at steelmaking temps"))))</f>
+        <v/>
+      </c>
+      <c r="L7" s="25" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6097,87 +7020,84 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F8" s="18" t="n">
-        <v>531.2981945804858</v>
-      </c>
-      <c r="G8" s="28" t="inlineStr">
-        <is>
-          <t>CANNOT reduce</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="F8" s="18">
+        <f>'Binary Screening'!H8</f>
+        <v/>
+      </c>
+      <c r="G8" s="17">
+        <f>'Binary Screening'!I8</f>
+        <v/>
+      </c>
+      <c r="H8" s="19" t="inlineStr">
         <is>
           <t>CuTiO3</t>
         </is>
       </c>
-      <c r="I8" s="65" t="n">
-        <v>-36.79236755437637</v>
-      </c>
-      <c r="J8" s="72" t="inlineStr">
-        <is>
-          <t>FAVORABLE</t>
-        </is>
-      </c>
-      <c r="K8" s="71" t="inlineStr">
-        <is>
-          <t>PROMISING — ternary compound forms</t>
-        </is>
-      </c>
-      <c r="L8" s="21" t="inlineStr">
+      <c r="I8" s="18">
+        <f>IFERROR('Ternary Reaction dG'!P10,"TBD")</f>
+        <v/>
+      </c>
+      <c r="J8" s="17">
+        <f>IF(NOT(ISNUMBER(I8)),"TBD",IF(I8&lt;-10,"FAVORABLE",IF(I8&lt;0,"Marginal",IF(I8&lt;10,"Borderline","Unfavorable"))))</f>
+        <v/>
+      </c>
+      <c r="K8" s="19">
+        <f>IF(NOT(ISNUMBER(I8)),"Awaiting ternary data",IF(I8&lt;-10,"PROMISING - ternary compound forms",IF(I8&lt;0,"Marginal - weak compound formation",IF(A8="CuO","Trivial - further Cu oxidation","Not promising at steelmaking temps"))))</f>
+        <v/>
+      </c>
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>SiO2</t>
         </is>
       </c>
-      <c r="B9" s="23" t="n">
+      <c r="B9" s="22" t="n">
         <v>2.65</v>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="22" t="n">
         <v>1713</v>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F9" s="24" t="n">
-        <v>502.720485707874</v>
-      </c>
-      <c r="G9" s="29" t="inlineStr">
-        <is>
-          <t>CANNOT reduce</t>
-        </is>
-      </c>
-      <c r="H9" s="26" t="inlineStr">
-        <is>
-          <t>Cu2SiO4</t>
-        </is>
-      </c>
-      <c r="I9" s="65" t="n">
-        <v>-52.2142038660238</v>
-      </c>
-      <c r="J9" s="70" t="inlineStr">
-        <is>
-          <t>FAVORABLE</t>
-        </is>
-      </c>
-      <c r="K9" s="71" t="inlineStr">
-        <is>
-          <t>PROMISING — ternary compound forms</t>
-        </is>
-      </c>
-      <c r="L9" s="27" t="inlineStr">
+      <c r="F9" s="23">
+        <f>'Binary Screening'!H9</f>
+        <v/>
+      </c>
+      <c r="G9" s="22">
+        <f>'Binary Screening'!I9</f>
+        <v/>
+      </c>
+      <c r="H9" s="24">
+        <f>IFERROR(INDEX('Ternary Reaction dG'!A11:A12,MATCH(MIN('Ternary Reaction dG'!P11:G12),'Ternary Reaction dG'!P11:G12,0)),"N/A")</f>
+        <v/>
+      </c>
+      <c r="I9" s="23">
+        <f>IFERROR(MIN('Ternary Reaction dG'!P11:G12),"TBD")</f>
+        <v/>
+      </c>
+      <c r="J9" s="22">
+        <f>IF(NOT(ISNUMBER(I9)),"TBD",IF(I9&lt;-10,"FAVORABLE",IF(I9&lt;0,"Marginal",IF(I9&lt;10,"Borderline","Unfavorable"))))</f>
+        <v/>
+      </c>
+      <c r="K9" s="24">
+        <f>IF(NOT(ISNUMBER(I9)),"Awaiting ternary data",IF(I9&lt;-10,"PROMISING - ternary compound forms",IF(I9&lt;0,"Marginal - weak compound formation",IF(A9="CuO","Trivial - further Cu oxidation","Not promising at steelmaking temps"))))</f>
+        <v/>
+      </c>
+      <c r="L9" s="25" t="inlineStr">
         <is>
           <t>Low (silicosis)</t>
         </is>
@@ -6205,87 +7125,85 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F10" s="18" t="n">
-        <v>408.894023554667</v>
-      </c>
-      <c r="G10" s="28" t="inlineStr">
-        <is>
-          <t>CANNOT reduce</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="F10" s="18">
+        <f>'Binary Screening'!H10</f>
+        <v/>
+      </c>
+      <c r="G10" s="17">
+        <f>'Binary Screening'!I10</f>
+        <v/>
+      </c>
+      <c r="H10" s="19" t="inlineStr">
         <is>
           <t>CuMn2O4</t>
         </is>
       </c>
-      <c r="I10" s="65" t="n">
-        <v>-64.44255177885806</v>
-      </c>
-      <c r="J10" s="72" t="inlineStr">
-        <is>
-          <t>FAVORABLE</t>
-        </is>
-      </c>
-      <c r="K10" s="71" t="inlineStr">
-        <is>
-          <t>PROMISING — ternary compound forms</t>
-        </is>
-      </c>
-      <c r="L10" s="21" t="inlineStr">
+      <c r="I10" s="18">
+        <f>IFERROR('Ternary Reaction dG'!P5,"TBD")</f>
+        <v/>
+      </c>
+      <c r="J10" s="17">
+        <f>IF(NOT(ISNUMBER(I10)),"TBD",IF(I10&lt;-10,"FAVORABLE",IF(I10&lt;0,"Marginal",IF(I10&lt;10,"Borderline","Unfavorable"))))</f>
+        <v/>
+      </c>
+      <c r="K10" s="19">
+        <f>IF(NOT(ISNUMBER(I10)),"Awaiting ternary data",IF(I10&lt;-10,"PROMISING - ternary compound forms",IF(I10&lt;0,"Marginal - weak compound formation",IF(A10="CuO","Trivial - further Cu oxidation","Not promising at steelmaking temps"))))</f>
+        <v/>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Cr2O3</t>
         </is>
       </c>
-      <c r="B11" s="23" t="n">
+      <c r="B11" s="22" t="n">
         <v>5.22</v>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="22" t="n">
         <v>2435</v>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F11" s="24" t="n">
-        <v>354.838962051855</v>
-      </c>
-      <c r="G11" s="29" t="inlineStr">
-        <is>
-          <t>CANNOT reduce</t>
-        </is>
-      </c>
-      <c r="H11" s="26" t="inlineStr">
+      <c r="F11" s="23">
+        <f>'Binary Screening'!H11</f>
+        <v/>
+      </c>
+      <c r="G11" s="22">
+        <f>'Binary Screening'!I11</f>
+        <v/>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
         <is>
           <t>CuCr2O4</t>
         </is>
       </c>
-      <c r="I11" s="65" t="n">
-        <v>-29.97263435832225</v>
-      </c>
-      <c r="J11" s="70" t="inlineStr">
-        <is>
-          <t>FAVORABLE</t>
-        </is>
-      </c>
-      <c r="K11" s="71" t="inlineStr">
-        <is>
-          <t>PROMISING — ternary compound forms</t>
-        </is>
-      </c>
-      <c r="L11" s="27" t="inlineStr">
+      <c r="I11" s="23">
+        <f>IFERROR('Ternary Reaction dG'!P4,"TBD")</f>
+        <v/>
+      </c>
+      <c r="J11" s="22">
+        <f>IF(NOT(ISNUMBER(I11)),"TBD",IF(I11&lt;-10,"FAVORABLE",IF(I11&lt;0,"Marginal",IF(I11&lt;10,"Borderline","Unfavorable"))))</f>
+        <v/>
+      </c>
+      <c r="K11" s="24">
+        <f>IF(NOT(ISNUMBER(I11)),"Awaiting ternary data",IF(I11&lt;-10,"PROMISING - ternary compound forms",IF(I11&lt;0,"Marginal - weak compound formation",IF(A11="CuO","Trivial - further Cu oxidation","Not promising at steelmaking temps"))))</f>
+        <v/>
+      </c>
+      <c r="L11" s="25" t="inlineStr">
         <is>
           <t>Moderate (Cr VI)</t>
         </is>
@@ -6308,92 +7226,89 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E12" s="28" t="inlineStr">
+      <c r="E12" s="26" t="inlineStr">
         <is>
           <t>LIQUID</t>
         </is>
       </c>
-      <c r="F12" s="18" t="n">
-        <v>259.4176758391675</v>
-      </c>
-      <c r="G12" s="28" t="inlineStr">
-        <is>
-          <t>CANNOT reduce</t>
-        </is>
-      </c>
-      <c r="H12" s="20" t="inlineStr">
-        <is>
-          <t>Cu3V2O8</t>
-        </is>
-      </c>
-      <c r="I12" s="65" t="n">
-        <v>-109.153739537538</v>
-      </c>
-      <c r="J12" s="72" t="inlineStr">
-        <is>
-          <t>FAVORABLE</t>
-        </is>
-      </c>
-      <c r="K12" s="71" t="inlineStr">
-        <is>
-          <t>PROMISING — ternary compound forms</t>
-        </is>
-      </c>
-      <c r="L12" s="21" t="inlineStr">
+      <c r="F12" s="18">
+        <f>'Binary Screening'!H12</f>
+        <v/>
+      </c>
+      <c r="G12" s="17">
+        <f>'Binary Screening'!I12</f>
+        <v/>
+      </c>
+      <c r="H12" s="19">
+        <f>IFERROR(INDEX('Ternary Reaction dG'!A8:A9,MATCH(MIN('Ternary Reaction dG'!P8:G9),'Ternary Reaction dG'!P8:G9,0)),"N/A")</f>
+        <v/>
+      </c>
+      <c r="I12" s="18">
+        <f>IFERROR(MIN('Ternary Reaction dG'!P8:G9),"TBD")</f>
+        <v/>
+      </c>
+      <c r="J12" s="17">
+        <f>IF(NOT(ISNUMBER(I12)),"TBD",IF(I12&lt;-10,"FAVORABLE",IF(I12&lt;0,"Marginal",IF(I12&lt;10,"Borderline","Unfavorable"))))</f>
+        <v/>
+      </c>
+      <c r="K12" s="19">
+        <f>IF(NOT(ISNUMBER(I12)),"Awaiting ternary data",IF(I12&lt;-10,"PROMISING - ternary compound forms",IF(I12&lt;0,"Marginal - weak compound formation",IF(A12="CuO","Trivial - further Cu oxidation","Not promising at steelmaking temps"))))</f>
+        <v/>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>HIGH - Carc. 1B</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>FeO</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n">
+      <c r="B13" s="22" t="n">
         <v>5.74</v>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C13" s="22" t="n">
         <v>1377</v>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E13" s="29" t="inlineStr">
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>LIQUID</t>
         </is>
       </c>
-      <c r="F13" s="24" t="n">
-        <v>213.8079839998335</v>
-      </c>
-      <c r="G13" s="29" t="inlineStr">
-        <is>
-          <t>CANNOT reduce</t>
-        </is>
-      </c>
-      <c r="H13" s="26" t="inlineStr">
+      <c r="F13" s="23">
+        <f>'Binary Screening'!H13</f>
+        <v/>
+      </c>
+      <c r="G13" s="22">
+        <f>'Binary Screening'!I13</f>
+        <v/>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
         <is>
           <t>CuFe2O4</t>
         </is>
       </c>
-      <c r="I13" s="65" t="n">
-        <v>-111.8803016055257</v>
-      </c>
-      <c r="J13" s="70" t="inlineStr">
-        <is>
-          <t>FAVORABLE</t>
-        </is>
-      </c>
-      <c r="K13" s="71" t="inlineStr">
-        <is>
-          <t>PROMISING — ternary compound forms</t>
-        </is>
-      </c>
-      <c r="L13" s="27" t="inlineStr">
+      <c r="I13" s="23">
+        <f>IFERROR('Ternary Reaction dG'!P6,"TBD")</f>
+        <v/>
+      </c>
+      <c r="J13" s="22">
+        <f>IF(NOT(ISNUMBER(I13)),"TBD",IF(I13&lt;-10,"FAVORABLE",IF(I13&lt;0,"Marginal",IF(I13&lt;10,"Borderline","Unfavorable"))))</f>
+        <v/>
+      </c>
+      <c r="K13" s="24">
+        <f>IF(NOT(ISNUMBER(I13)),"Awaiting ternary data",IF(I13&lt;-10,"PROMISING - ternary compound forms",IF(I13&lt;0,"Marginal - weak compound formation",IF(A13="CuO","Trivial - further Cu oxidation","Not promising at steelmaking temps"))))</f>
+        <v/>
+      </c>
+      <c r="L13" s="25" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6421,87 +7336,85 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F14" s="18" t="n">
-        <v>126.618759676311</v>
-      </c>
-      <c r="G14" s="28" t="inlineStr">
-        <is>
-          <t>CANNOT reduce</t>
-        </is>
-      </c>
-      <c r="H14" s="20" t="inlineStr">
+      <c r="F14" s="18">
+        <f>'Binary Screening'!H14</f>
+        <v/>
+      </c>
+      <c r="G14" s="17">
+        <f>'Binary Screening'!I14</f>
+        <v/>
+      </c>
+      <c r="H14" s="19" t="inlineStr">
         <is>
           <t>CuCo2O4</t>
         </is>
       </c>
-      <c r="I14" s="65" t="n">
-        <v>-35.78728833140316</v>
-      </c>
-      <c r="J14" s="72" t="inlineStr">
-        <is>
-          <t>FAVORABLE</t>
-        </is>
-      </c>
-      <c r="K14" s="71" t="inlineStr">
-        <is>
-          <t>PROMISING — ternary compound forms</t>
-        </is>
-      </c>
-      <c r="L14" s="21" t="inlineStr">
+      <c r="I14" s="18">
+        <f>IFERROR('Ternary Reaction dG'!P7,"TBD")</f>
+        <v/>
+      </c>
+      <c r="J14" s="17">
+        <f>IF(NOT(ISNUMBER(I14)),"TBD",IF(I14&lt;-10,"FAVORABLE",IF(I14&lt;0,"Marginal",IF(I14&lt;10,"Borderline","Unfavorable"))))</f>
+        <v/>
+      </c>
+      <c r="K14" s="19">
+        <f>IF(NOT(ISNUMBER(I14)),"Awaiting ternary data",IF(I14&lt;-10,"PROMISING - ternary compound forms",IF(I14&lt;0,"Marginal - weak compound formation",IF(A14="CuO","Trivial - further Cu oxidation","Not promising at steelmaking temps"))))</f>
+        <v/>
+      </c>
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>HIGH - Carc. 1B</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>NiO</t>
         </is>
       </c>
-      <c r="B15" s="23" t="n">
+      <c r="B15" s="22" t="n">
         <v>6.67</v>
       </c>
-      <c r="C15" s="23" t="n">
+      <c r="C15" s="22" t="n">
         <v>1955</v>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F15" s="24" t="n">
-        <v>76.02293325153424</v>
-      </c>
-      <c r="G15" s="29" t="inlineStr">
-        <is>
-          <t>CANNOT reduce</t>
-        </is>
-      </c>
-      <c r="H15" s="26" t="inlineStr">
+      <c r="F15" s="23">
+        <f>'Binary Screening'!H15</f>
+        <v/>
+      </c>
+      <c r="G15" s="22">
+        <f>'Binary Screening'!I15</f>
+        <v/>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
         <is>
           <t>CuNiO2</t>
         </is>
       </c>
-      <c r="I15" s="65" t="n">
-        <v>-27.33363264363294</v>
-      </c>
-      <c r="J15" s="70" t="inlineStr">
-        <is>
-          <t>FAVORABLE</t>
-        </is>
-      </c>
-      <c r="K15" s="71" t="inlineStr">
-        <is>
-          <t>PROMISING — ternary compound forms</t>
-        </is>
-      </c>
-      <c r="L15" s="27" t="inlineStr">
+      <c r="I15" s="23">
+        <f>IFERROR('Ternary Reaction dG'!P16,"TBD")</f>
+        <v/>
+      </c>
+      <c r="J15" s="22">
+        <f>IF(NOT(ISNUMBER(I15)),"TBD",IF(I15&lt;-10,"FAVORABLE",IF(I15&lt;0,"Marginal",IF(I15&lt;10,"Borderline","Unfavorable"))))</f>
+        <v/>
+      </c>
+      <c r="K15" s="24">
+        <f>IF(NOT(ISNUMBER(I15)),"Awaiting ternary data",IF(I15&lt;-10,"PROMISING - ternary compound forms",IF(I15&lt;0,"Marginal - weak compound formation",IF(A15="CuO","Trivial - further Cu oxidation","Not promising at steelmaking temps"))))</f>
+        <v/>
+      </c>
+      <c r="L15" s="25" t="inlineStr">
         <is>
           <t>HIGH - IARC Grp 1</t>
         </is>
@@ -6524,25 +7437,25 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E16" s="28" t="inlineStr">
+      <c r="E16" s="26" t="inlineStr">
         <is>
           <t>LIQUID</t>
         </is>
       </c>
-      <c r="F16" s="18" t="n">
-        <v>136.1552920352077</v>
-      </c>
-      <c r="G16" s="28" t="inlineStr">
-        <is>
-          <t>CANNOT reduce</t>
-        </is>
-      </c>
-      <c r="H16" s="20" t="inlineStr">
+      <c r="F16" s="18">
+        <f>'Binary Screening'!H16</f>
+        <v/>
+      </c>
+      <c r="G16" s="17">
+        <f>'Binary Screening'!I16</f>
+        <v/>
+      </c>
+      <c r="H16" s="19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I16" s="31" t="inlineStr">
+      <c r="I16" s="100" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
@@ -6552,122 +7465,121 @@
           <t>Not modeled</t>
         </is>
       </c>
-      <c r="K16" s="20" t="inlineStr">
-        <is>
-          <t>Binary only — no ternary model</t>
-        </is>
-      </c>
-      <c r="L16" s="21" t="inlineStr">
+      <c r="K16" s="19" t="inlineStr">
+        <is>
+          <t>Awaiting ternary data</t>
+        </is>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>HIGH - neurotoxin</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>B2O3</t>
         </is>
       </c>
-      <c r="B17" s="23" t="n">
+      <c r="B17" s="22" t="n">
         <v>2.55</v>
       </c>
-      <c r="C17" s="23" t="n">
+      <c r="C17" s="22" t="n">
         <v>450</v>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E17" s="29" t="inlineStr">
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t>LIQUID</t>
         </is>
       </c>
-      <c r="F17" s="24" t="n">
-        <v>481.1041698284617</v>
-      </c>
-      <c r="G17" s="29" t="inlineStr">
-        <is>
-          <t>CANNOT reduce</t>
-        </is>
-      </c>
-      <c r="H17" s="26" t="inlineStr">
+      <c r="F17" s="23">
+        <f>'Binary Screening'!H17</f>
+        <v/>
+      </c>
+      <c r="G17" s="22">
+        <f>'Binary Screening'!I17</f>
+        <v/>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
         <is>
           <t>CuB2O4</t>
         </is>
       </c>
-      <c r="I17" s="65" t="n">
-        <v>-47.71152449032571</v>
-      </c>
-      <c r="J17" s="70" t="inlineStr">
-        <is>
-          <t>FAVORABLE</t>
-        </is>
-      </c>
-      <c r="K17" s="71" t="inlineStr">
-        <is>
-          <t>PROMISING — ternary compound forms</t>
-        </is>
-      </c>
-      <c r="L17" s="27" t="inlineStr">
+      <c r="I17" s="23">
+        <f>IFERROR('Ternary Reaction dG'!P19,"TBD")</f>
+        <v/>
+      </c>
+      <c r="J17" s="22">
+        <f>IF(NOT(ISNUMBER(I17)),"TBD",IF(I17&lt;-10,"FAVORABLE",IF(I17&lt;0,"Marginal",IF(I17&lt;10,"Borderline","Unfavorable"))))</f>
+        <v/>
+      </c>
+      <c r="K17" s="24">
+        <f>IF(NOT(ISNUMBER(I17)),"Awaiting ternary data",IF(I17&lt;-10,"PROMISING - ternary compound forms",IF(I17&lt;0,"Marginal - weak compound formation",IF(A17="CuO","Trivial - further Cu oxidation","Not promising at steelmaking temps"))))</f>
+        <v/>
+      </c>
+      <c r="L17" s="25" t="inlineStr">
         <is>
           <t>Moderate - Repr.1B</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>CuO</t>
         </is>
       </c>
-      <c r="B18" s="33" t="n">
+      <c r="B18" s="29" t="n">
         <v>6.31</v>
       </c>
-      <c r="C18" s="33" t="n">
+      <c r="C18" s="29" t="n">
         <v>1326</v>
       </c>
-      <c r="D18" s="33" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E18" s="34" t="inlineStr">
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t>LIQUID</t>
         </is>
       </c>
-      <c r="F18" s="35" t="n">
-        <v>-40.99015583836951</v>
-      </c>
-      <c r="G18" s="73" t="inlineStr">
-        <is>
-          <t>CAN reduce</t>
-        </is>
-      </c>
-      <c r="H18" s="36" t="inlineStr">
+      <c r="F18" s="31">
+        <f>'Binary Screening'!H18</f>
+        <v/>
+      </c>
+      <c r="G18" s="29">
+        <f>'Binary Screening'!I18</f>
+        <v/>
+      </c>
+      <c r="H18" s="32" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I18" s="74" t="inlineStr">
+      <c r="I18" s="101" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="J18" s="33" t="inlineStr">
+      <c r="J18" s="29" t="inlineStr">
         <is>
           <t>Not modeled</t>
         </is>
       </c>
-      <c r="K18" s="36" t="inlineStr">
-        <is>
-          <t>Trivial — further Cu oxidation</t>
-        </is>
-      </c>
-      <c r="L18" s="37" t="inlineStr">
+      <c r="K18" s="32" t="inlineStr">
+        <is>
+          <t>Trivial - further Cu oxidation</t>
+        </is>
+      </c>
+      <c r="L18" s="33" t="inlineStr">
         <is>
           <t>Moderate - aquatic</t>
         </is>
@@ -6697,25 +7609,55 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>"Best Ternary Product" is the compound with the most negative dG at 1527C.</t>
+          <t>FORMULA CELLS: Col F refs 'Binary Screening', Col I refs 'Ternary Reaction dG'.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>PROMISING oxides capture Cu into ternary compounds even though Cu cannot reduce them directly.</t>
+          <t>Cols G, H, J, K are formulas (cross-tab refs or IF() verdicts).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
+          <t>Total formula cells in this tab: 82.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>PROMISING oxides capture Cu into ternary compounds even though Cu cannot reduce them directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
           <t>This is the key insight: reduction is impossible, but compound formation may be favorable.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="F2:F18">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThanOrEqual" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I18">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="4">
+      <formula>-10</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6743,28 +7685,28 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="75" t="inlineStr">
+      <c r="A3" s="102" t="inlineStr">
         <is>
           <t>Thermo-Calc reports GM = Gibbs energy per mole of ATOMS</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="75" t="inlineStr">
+      <c r="A4" s="102" t="inlineStr">
         <is>
           <t>We need: dGf per mole of O2 (for Ellingham comparison)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="75" t="inlineStr">
+      <c r="A6" s="102" t="inlineStr">
         <is>
           <t>Step 1: GM (J/mol atoms) x atoms_per_formula = G per formula unit</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="75" t="inlineStr">
+      <c r="A7" s="102" t="inlineStr">
         <is>
           <t>Step 2: G per formula / oxide_per_O2 = dGf per mol O2</t>
         </is>
@@ -6800,7 +7742,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="76" t="inlineStr">
+      <c r="A11" s="103" t="inlineStr">
         <is>
           <t>Cu2O</t>
         </is>
@@ -6808,7 +7750,7 @@
       <c r="B11" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>4Cu + O2 -&gt; 2Cu2O</t>
         </is>
@@ -6818,15 +7760,15 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="77" t="inlineStr">
+      <c r="A12" s="104" t="inlineStr">
         <is>
           <t>Al2O3</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n">
+      <c r="B12" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>4/3 Al + O2 -&gt; 2/3 Al2O3</t>
         </is>
@@ -6836,7 +7778,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="76" t="inlineStr">
+      <c r="A13" s="103" t="inlineStr">
         <is>
           <t>MgO</t>
         </is>
@@ -6844,7 +7786,7 @@
       <c r="B13" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>2Mg + O2 -&gt; 2MgO</t>
         </is>
@@ -6854,15 +7796,15 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="77" t="inlineStr">
+      <c r="A14" s="104" t="inlineStr">
         <is>
           <t>SiO2</t>
         </is>
       </c>
-      <c r="B14" s="23" t="n">
+      <c r="B14" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>Si + O2 -&gt; SiO2</t>
         </is>
@@ -6872,7 +7814,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="76" t="inlineStr">
+      <c r="A15" s="103" t="inlineStr">
         <is>
           <t>TiO2</t>
         </is>
@@ -6880,7 +7822,7 @@
       <c r="B15" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>Ti + O2 -&gt; TiO2</t>
         </is>
@@ -6890,15 +7832,15 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="77" t="inlineStr">
+      <c r="A16" s="104" t="inlineStr">
         <is>
           <t>FeO</t>
         </is>
       </c>
-      <c r="B16" s="23" t="n">
+      <c r="B16" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>2Fe + O2 -&gt; 2FeO</t>
         </is>
@@ -6908,7 +7850,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="76" t="inlineStr">
+      <c r="A17" s="103" t="inlineStr">
         <is>
           <t>CaO</t>
         </is>
@@ -6916,7 +7858,7 @@
       <c r="B17" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>2Ca + O2 -&gt; 2CaO</t>
         </is>
@@ -6926,15 +7868,15 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="77" t="inlineStr">
+      <c r="A18" s="104" t="inlineStr">
         <is>
           <t>ZrO2</t>
         </is>
       </c>
-      <c r="B18" s="23" t="n">
+      <c r="B18" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>Zr + O2 -&gt; ZrO2</t>
         </is>
@@ -6944,7 +7886,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="76" t="inlineStr">
+      <c r="A19" s="103" t="inlineStr">
         <is>
           <t>Cr2O3</t>
         </is>
@@ -6952,7 +7894,7 @@
       <c r="B19" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>4/3 Cr + O2 -&gt; 2/3 Cr2O3</t>
         </is>
@@ -6962,15 +7904,15 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="77" t="inlineStr">
+      <c r="A20" s="104" t="inlineStr">
         <is>
           <t>MnO</t>
         </is>
       </c>
-      <c r="B20" s="23" t="n">
+      <c r="B20" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>2Mn + O2 -&gt; 2MnO</t>
         </is>
@@ -6980,7 +7922,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="A21" s="103" t="inlineStr">
         <is>
           <t>V2O5</t>
         </is>
@@ -6988,7 +7930,7 @@
       <c r="B21" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>4/5 V + O2 -&gt; 2/5 V2O5</t>
         </is>
@@ -6998,15 +7940,15 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="77" t="inlineStr">
+      <c r="A22" s="104" t="inlineStr">
         <is>
           <t>B2O3</t>
         </is>
       </c>
-      <c r="B22" s="23" t="n">
+      <c r="B22" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>4/3 B + O2 -&gt; 2/3 B2O3</t>
         </is>
@@ -7016,7 +7958,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="76" t="inlineStr">
+      <c r="A23" s="103" t="inlineStr">
         <is>
           <t>La2O3</t>
         </is>
@@ -7024,7 +7966,7 @@
       <c r="B23" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>4/3 La + O2 -&gt; 2/3 La2O3</t>
         </is>
@@ -7034,15 +7976,15 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="77" t="inlineStr">
+      <c r="A24" s="104" t="inlineStr">
         <is>
           <t>CeO2</t>
         </is>
       </c>
-      <c r="B24" s="23" t="n">
+      <c r="B24" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>Ce + O2 -&gt; CeO2</t>
         </is>
@@ -7052,7 +7994,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="76" t="inlineStr">
+      <c r="A25" s="103" t="inlineStr">
         <is>
           <t>NiO</t>
         </is>
@@ -7060,7 +8002,7 @@
       <c r="B25" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>2Ni + O2 -&gt; 2NiO</t>
         </is>
@@ -7070,15 +8012,15 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="77" t="inlineStr">
+      <c r="A26" s="104" t="inlineStr">
         <is>
           <t>CoO</t>
         </is>
       </c>
-      <c r="B26" s="23" t="n">
+      <c r="B26" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="C26" s="26" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>2Co + O2 -&gt; 2CoO</t>
         </is>
@@ -7088,15 +8030,15 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="78" t="inlineStr">
+      <c r="A27" s="105" t="inlineStr">
         <is>
           <t>PbO</t>
         </is>
       </c>
-      <c r="B27" s="33" t="n">
+      <c r="B27" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="C27" s="36" t="inlineStr">
+      <c r="C27" s="32" t="inlineStr">
         <is>
           <t>2Pb + O2 -&gt; 2PbO</t>
         </is>
@@ -7170,10 +8112,10 @@
           <t>1306-38-3</t>
         </is>
       </c>
-      <c r="C2" s="79" t="n">
+      <c r="C2" s="106" t="n">
         <v>0.9</v>
       </c>
-      <c r="D2" s="80" t="n">
+      <c r="D2" s="107" t="n">
         <v>0.006</v>
       </c>
       <c r="E2" s="17" t="inlineStr">
@@ -7181,35 +8123,35 @@
           <t>211575</t>
         </is>
       </c>
-      <c r="F2" s="21" t="inlineStr">
+      <c r="F2" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>CaO</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>1305-78-8</t>
         </is>
       </c>
-      <c r="C3" s="81" t="n">
+      <c r="C3" s="108" t="n">
         <v>0.16</v>
       </c>
-      <c r="D3" s="82" t="n">
+      <c r="D3" s="109" t="n">
         <v>0.0002</v>
       </c>
-      <c r="E3" s="23" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>248568</t>
         </is>
       </c>
-      <c r="F3" s="27" t="inlineStr">
+      <c r="F3" s="25" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7226,10 +8168,10 @@
           <t>1312-81-8</t>
         </is>
       </c>
-      <c r="C4" s="79" t="n">
+      <c r="C4" s="106" t="n">
         <v>1.25</v>
       </c>
-      <c r="D4" s="80" t="n">
+      <c r="D4" s="107" t="n">
         <v>0.01</v>
       </c>
       <c r="E4" s="17" t="inlineStr">
@@ -7237,35 +8179,35 @@
           <t>L4000</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>Low-Moderate</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>MgO</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>1309-48-4</t>
         </is>
       </c>
-      <c r="C5" s="81" t="n">
+      <c r="C5" s="108" t="n">
         <v>0.13</v>
       </c>
-      <c r="D5" s="82" t="n">
+      <c r="D5" s="109" t="n">
         <v>0.0003</v>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>529699</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7282,10 +8224,10 @@
           <t>1314-23-4</t>
         </is>
       </c>
-      <c r="C6" s="79" t="n">
+      <c r="C6" s="106" t="n">
         <v>0.67</v>
       </c>
-      <c r="D6" s="80" t="n">
+      <c r="D6" s="107" t="n">
         <v>0.035</v>
       </c>
       <c r="E6" s="17" t="inlineStr">
@@ -7293,35 +8235,35 @@
           <t>230693</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Al2O3</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>1344-28-1</t>
         </is>
       </c>
-      <c r="C7" s="81" t="n">
+      <c r="C7" s="108" t="n">
         <v>0.09</v>
       </c>
-      <c r="D7" s="82" t="n">
+      <c r="D7" s="109" t="n">
         <v>0.0005</v>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>11028</t>
         </is>
       </c>
-      <c r="F7" s="27" t="inlineStr">
+      <c r="F7" s="25" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7338,10 +8280,10 @@
           <t>13463-67-7</t>
         </is>
       </c>
-      <c r="C8" s="79" t="n">
+      <c r="C8" s="106" t="n">
         <v>0.29</v>
       </c>
-      <c r="D8" s="80" t="n">
+      <c r="D8" s="107" t="n">
         <v>0.003</v>
       </c>
       <c r="E8" s="17" t="inlineStr">
@@ -7349,35 +8291,35 @@
           <t>14021</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>SiO2</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>7631-86-9</t>
         </is>
       </c>
-      <c r="C9" s="81" t="n">
+      <c r="C9" s="108" t="n">
         <v>0.1</v>
       </c>
-      <c r="D9" s="82" t="n">
+      <c r="D9" s="109" t="n">
         <v>5e-05</v>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>637238</t>
         </is>
       </c>
-      <c r="F9" s="27" t="inlineStr">
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t>Low (silicosis)</t>
         </is>
@@ -7394,10 +8336,10 @@
           <t>1344-43-0</t>
         </is>
       </c>
-      <c r="C10" s="79" t="n">
+      <c r="C10" s="106" t="n">
         <v>0.55</v>
       </c>
-      <c r="D10" s="80" t="n">
+      <c r="D10" s="107" t="n">
         <v>0.005</v>
       </c>
       <c r="E10" s="17" t="inlineStr">
@@ -7405,35 +8347,35 @@
           <t>377201</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Cr2O3</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>1308-38-9</t>
         </is>
       </c>
-      <c r="C11" s="81" t="n">
+      <c r="C11" s="108" t="n">
         <v>2.38</v>
       </c>
-      <c r="D11" s="82" t="n">
+      <c r="D11" s="109" t="n">
         <v>0.005</v>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>393703</t>
         </is>
       </c>
-      <c r="F11" s="27" t="inlineStr">
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>Moderate (Cr VI)</t>
         </is>
@@ -7450,10 +8392,10 @@
           <t>1314-62-1</t>
         </is>
       </c>
-      <c r="C12" s="79" t="n">
+      <c r="C12" s="106" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="80" t="n">
+      <c r="D12" s="107" t="n">
         <v>0.011</v>
       </c>
       <c r="E12" s="17" t="inlineStr">
@@ -7461,35 +8403,35 @@
           <t>221899</t>
         </is>
       </c>
-      <c r="F12" s="83" t="inlineStr">
+      <c r="F12" s="110" t="inlineStr">
         <is>
           <t>HIGH - Carc. 1B</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>FeO</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>1345-25-1</t>
         </is>
       </c>
-      <c r="C13" s="81" t="n">
+      <c r="C13" s="108" t="n">
         <v>0.75</v>
       </c>
-      <c r="D13" s="82" t="n">
+      <c r="D13" s="109" t="n">
         <v>0.0009</v>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>400866</t>
         </is>
       </c>
-      <c r="F13" s="27" t="inlineStr">
+      <c r="F13" s="25" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7506,10 +8448,10 @@
           <t>1307-96-6</t>
         </is>
       </c>
-      <c r="C14" s="79" t="n">
+      <c r="C14" s="106" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="80" t="n">
+      <c r="D14" s="107" t="n">
         <v>0.018</v>
       </c>
       <c r="E14" s="17" t="inlineStr">
@@ -7517,35 +8459,35 @@
           <t>529443</t>
         </is>
       </c>
-      <c r="F14" s="83" t="inlineStr">
+      <c r="F14" s="110" t="inlineStr">
         <is>
           <t>HIGH - Carc. 1B</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>NiO</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>1313-99-1</t>
         </is>
       </c>
-      <c r="C15" s="81" t="n">
+      <c r="C15" s="108" t="n">
         <v>0.7</v>
       </c>
-      <c r="D15" s="82" t="n">
+      <c r="D15" s="109" t="n">
         <v>0.016</v>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>203882</t>
         </is>
       </c>
-      <c r="F15" s="84" t="inlineStr">
+      <c r="F15" s="111" t="inlineStr">
         <is>
           <t>HIGH - IARC Grp 1</t>
         </is>
@@ -7562,10 +8504,10 @@
           <t>1317-36-8</t>
         </is>
       </c>
-      <c r="C16" s="79" t="n">
+      <c r="C16" s="106" t="n">
         <v>0.26</v>
       </c>
-      <c r="D16" s="80" t="n">
+      <c r="D16" s="107" t="n">
         <v>0.004</v>
       </c>
       <c r="E16" s="17" t="inlineStr">
@@ -7573,35 +8515,35 @@
           <t>211907</t>
         </is>
       </c>
-      <c r="F16" s="83" t="inlineStr">
+      <c r="F16" s="110" t="inlineStr">
         <is>
           <t>HIGH - neurotoxin</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>Cu2O</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>1317-39-1</t>
         </is>
       </c>
-      <c r="C17" s="81" t="n">
+      <c r="C17" s="108" t="n">
         <v>0.34</v>
       </c>
-      <c r="D17" s="82" t="n">
+      <c r="D17" s="109" t="n">
         <v>0.008</v>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>208825</t>
         </is>
       </c>
-      <c r="F17" s="27" t="inlineStr">
+      <c r="F17" s="25" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
@@ -7618,10 +8560,10 @@
           <t>1317-38-0</t>
         </is>
       </c>
-      <c r="C18" s="79" t="n">
+      <c r="C18" s="106" t="n">
         <v>0.38</v>
       </c>
-      <c r="D18" s="80" t="n">
+      <c r="D18" s="107" t="n">
         <v>0.008</v>
       </c>
       <c r="E18" s="17" t="inlineStr">
@@ -7629,35 +8571,35 @@
           <t>208841</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>Moderate - aquatic</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="52" t="inlineStr">
+      <c r="A19" s="46" t="inlineStr">
         <is>
           <t>B2O3</t>
         </is>
       </c>
-      <c r="B19" s="54" t="inlineStr">
+      <c r="B19" s="48" t="inlineStr">
         <is>
           <t>1303-86-2</t>
         </is>
       </c>
-      <c r="C19" s="85" t="n">
+      <c r="C19" s="112" t="n">
         <v>1.09</v>
       </c>
-      <c r="D19" s="86" t="n">
+      <c r="D19" s="113" t="n">
         <v>0.003</v>
       </c>
-      <c r="E19" s="54" t="inlineStr">
+      <c r="E19" s="48" t="inlineStr">
         <is>
           <t>339075</t>
         </is>
       </c>
-      <c r="F19" s="66" t="inlineStr">
+      <c r="F19" s="86" t="inlineStr">
         <is>
           <t>Moderate - Repr.1B</t>
         </is>
